--- a/Treinamento/Index/Relatório de Recusas 02.02.2026 a 08.02.2026.xlsx
+++ b/Treinamento/Index/Relatório de Recusas 02.02.2026 a 08.02.2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29721"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/shirlei_witkowski_allianz_com_br/Documents/Planilha de recusa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3568EC12-5E82-4158-9B59-DAC8F36FAC99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF40FDD9-BB9E-4F8D-B9EF-604FA10630A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="02.02" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="158">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -450,6 +450,112 @@
   </si>
   <si>
     <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: FRENTE, MOTOR (LATERAL ESQUERDA) (NAO TIROU FOTO DO PASSO SOLICITADO) CARENAGEM LAT. DIR. ARR.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO ROBERTO HOLANDA DE ALMEIDA             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falta de vistoria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAIQUE NUNES PEREIRA                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">THAIS DE OLIVEIRA DIAS                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADRIANA APARECIDA COSTA DE OLIVEIRA          </t>
+  </si>
+  <si>
+    <t>Bloqueio recusado devido ao parecer da vistoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO RENATO DE SOUZA NUNES                  </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Chassi (Local incorreto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIEGO MARTINS NADAL                          </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 02.02.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIELE MAIA ALVES                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLA DOS SANTOS NOGUEIRA                    </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Frente e lateral do passageiro e mot, Traseira e lateral do passageiro e mot com a placa, Chassi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALDIR APARECIDA DA COSTA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRISCILA TOSCANO DE LIMA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCELO DE OLIVEIRA SILVA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERCEDES PARMIGIANI FIORAVANTE               </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que
+a apólice consta ativa na congênere, para que possamos prossegui
+r coma liberação do bloqueio será necessário a apresentação do e
+ndosso de cancelamento emitido, a atualização junto a Central de B
+ônus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAREN CRISTINA APARECIDA FERRAZ              </t>
+  </si>
+  <si>
+    <t>FRUSTRADA: CLIENTE NÃO CORRIGIU A FOTO INCORRETA - PRAZO EXPIRADO. FOTO INCORRETA: CHASSI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DARCISIO JOSE DA SILVA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDERSON ALEXANDRE DE PAULA MOTA             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROBERTO VALTER RODRIGUES JUNIOR              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOUGLAS EMANOEL FIRMINO DO VALE              </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: CHASSI (LOCAL INCORRETO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PNEUFER FERRAMENTAS E PNEUS LTDA EPP         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSSET IMPLEMENTOS AMBIENTAIS LTDA EPP       </t>
+  </si>
+  <si>
+    <t>RECUSA - Cliente não retornou com a foto do porta-malas aberto e vazio. Impossibilitando visualizar o fundo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VANESSA BISPO DA SILVA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WANDERSON PAULINO DO NASCIMENTO              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FELIPE CESAR LOPES GUIMARAES                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAARA KAYANA NORMANDO DA SILVA               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDRE SANTOS DE JESUS                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRUNO BERNARDINO CAVAZZANI                   </t>
   </si>
 </sst>
 </file>
@@ -498,7 +604,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -587,30 +693,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -621,17 +703,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -661,17 +732,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -680,17 +740,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -728,12 +777,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -772,20 +850,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -802,72 +868,66 @@
     <xf numFmtId="14" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1253,25 +1313,25 @@
       <c r="B2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D2" s="49" t="s">
+      <c r="C2" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D2" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="39">
+      <c r="E2" s="32">
         <v>3450236724</v>
       </c>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="30" t="s">
+      <c r="H2" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="I2" s="25" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1282,25 +1342,25 @@
       <c r="B3" s="7">
         <v>46048</v>
       </c>
-      <c r="C3" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D3" s="51">
+      <c r="C3" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D3" s="16">
         <v>136324853</v>
       </c>
       <c r="E3" s="15">
         <v>3450223227</v>
       </c>
-      <c r="F3" s="47" t="s">
+      <c r="F3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="48" t="s">
+      <c r="G3" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="52" t="s">
+      <c r="H3" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="29">
+      <c r="I3" s="25">
         <v>46045</v>
       </c>
     </row>
@@ -1311,25 +1371,25 @@
       <c r="B4" s="7">
         <v>46042</v>
       </c>
-      <c r="C4" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D4" s="51">
+      <c r="C4" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D4" s="16">
         <v>136335481</v>
       </c>
       <c r="E4" s="15">
         <v>3450224063</v>
       </c>
-      <c r="F4" s="47" t="s">
+      <c r="F4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="48" t="s">
+      <c r="G4" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="52" t="s">
+      <c r="H4" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="29">
+      <c r="I4" s="25">
         <v>46048</v>
       </c>
     </row>
@@ -1340,25 +1400,25 @@
       <c r="B5" s="7">
         <v>46043</v>
       </c>
-      <c r="C5" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D5" s="51">
+      <c r="C5" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D5" s="16">
         <v>136351044</v>
       </c>
       <c r="E5" s="15">
         <v>3450225141</v>
       </c>
-      <c r="F5" s="47" t="s">
+      <c r="F5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="48" t="s">
+      <c r="G5" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="30" t="s">
+      <c r="H5" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="29">
+      <c r="I5" s="25">
         <v>46043</v>
       </c>
     </row>
@@ -1369,25 +1429,25 @@
       <c r="B6" s="7">
         <v>46042</v>
       </c>
-      <c r="C6" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D6" s="51">
+      <c r="C6" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D6" s="16">
         <v>136344079</v>
       </c>
       <c r="E6" s="15">
         <v>3450224019</v>
       </c>
-      <c r="F6" s="47" t="s">
+      <c r="F6" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="48" t="s">
+      <c r="G6" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="30" t="s">
+      <c r="H6" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="29">
+      <c r="I6" s="25">
         <v>46042</v>
       </c>
     </row>
@@ -1398,25 +1458,25 @@
       <c r="B7" s="7">
         <v>46043</v>
       </c>
-      <c r="C7" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D7" s="51">
+      <c r="C7" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D7" s="16">
         <v>136346831</v>
       </c>
       <c r="E7" s="15">
         <v>3450224712</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="F7" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="48" t="s">
+      <c r="G7" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="30" t="s">
+      <c r="H7" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="25">
         <v>46052</v>
       </c>
     </row>
@@ -1427,25 +1487,25 @@
       <c r="B8" s="7">
         <v>46043</v>
       </c>
-      <c r="C8" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D8" s="51">
+      <c r="C8" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D8" s="16">
         <v>136350580</v>
       </c>
       <c r="E8" s="15">
         <v>3450225086</v>
       </c>
-      <c r="F8" s="47" t="s">
+      <c r="F8" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="48" t="s">
+      <c r="G8" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="52" t="s">
+      <c r="H8" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="I8" s="29">
+      <c r="I8" s="25">
         <v>46048</v>
       </c>
     </row>
@@ -1456,25 +1516,25 @@
       <c r="B9" s="7">
         <v>46043</v>
       </c>
-      <c r="C9" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D9" s="51">
+      <c r="C9" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D9" s="16">
         <v>136354010</v>
       </c>
       <c r="E9" s="15">
         <v>3450225350</v>
       </c>
-      <c r="F9" s="47" t="s">
+      <c r="F9" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="48" t="s">
+      <c r="G9" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="52" t="s">
+      <c r="H9" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="I9" s="29">
+      <c r="I9" s="25">
         <v>46055</v>
       </c>
     </row>
@@ -1485,25 +1545,25 @@
       <c r="B10" s="7">
         <v>46045</v>
       </c>
-      <c r="C10" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D10" s="51">
+      <c r="C10" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D10" s="16">
         <v>136372495</v>
       </c>
-      <c r="E10" s="53" t="s">
+      <c r="E10" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="47" t="s">
+      <c r="F10" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="48" t="s">
+      <c r="G10" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="30" t="s">
+      <c r="H10" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="29">
+      <c r="I10" s="25">
         <v>46049</v>
       </c>
     </row>
@@ -1514,25 +1574,25 @@
       <c r="B11" s="7">
         <v>46044</v>
       </c>
-      <c r="C11" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D11" s="51">
+      <c r="C11" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D11" s="16">
         <v>136370002</v>
       </c>
       <c r="E11" s="15">
         <v>3450226560</v>
       </c>
-      <c r="F11" s="47" t="s">
+      <c r="F11" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="G11" s="48" t="s">
+      <c r="G11" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="30" t="s">
+      <c r="H11" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="I11" s="29">
+      <c r="I11" s="25">
         <v>46055</v>
       </c>
     </row>
@@ -1543,25 +1603,25 @@
       <c r="B12" s="7">
         <v>46044</v>
       </c>
-      <c r="C12" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D12" s="51">
+      <c r="C12" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D12" s="16">
         <v>136372234</v>
       </c>
       <c r="E12" s="15">
         <v>3450226824</v>
       </c>
-      <c r="F12" s="47" t="s">
+      <c r="F12" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="48" t="s">
+      <c r="G12" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="H12" s="30" t="s">
+      <c r="H12" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="29">
+      <c r="I12" s="25">
         <v>46044</v>
       </c>
     </row>
@@ -1572,25 +1632,25 @@
       <c r="B13" s="7">
         <v>46044</v>
       </c>
-      <c r="C13" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D13" s="51">
+      <c r="C13" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D13" s="16">
         <v>136371166</v>
       </c>
       <c r="E13" s="15">
         <v>3450226692</v>
       </c>
-      <c r="F13" s="47" t="s">
+      <c r="F13" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="48" t="s">
+      <c r="G13" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="H13" s="30" t="s">
+      <c r="H13" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="I13" s="29">
+      <c r="I13" s="25">
         <v>46052</v>
       </c>
     </row>
@@ -1601,25 +1661,25 @@
       <c r="B14" s="7">
         <v>46043</v>
       </c>
-      <c r="C14" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D14" s="51">
+      <c r="C14" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D14" s="16">
         <v>136349598</v>
       </c>
       <c r="E14" s="15">
         <v>3450225009</v>
       </c>
-      <c r="F14" s="47" t="s">
+      <c r="F14" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="G14" s="48" t="s">
+      <c r="G14" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="H14" s="30" t="s">
+      <c r="H14" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="I14" s="29">
+      <c r="I14" s="25">
         <v>46043</v>
       </c>
     </row>
@@ -1630,25 +1690,25 @@
       <c r="B15" s="7">
         <v>46048</v>
       </c>
-      <c r="C15" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D15" s="51">
+      <c r="C15" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D15" s="16">
         <v>136404984</v>
       </c>
       <c r="E15" s="15">
         <v>3450229420</v>
       </c>
-      <c r="F15" s="47" t="s">
+      <c r="F15" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="G15" s="48" t="s">
+      <c r="G15" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="H15" s="30" t="s">
+      <c r="H15" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="I15" s="29">
+      <c r="I15" s="25">
         <v>46048</v>
       </c>
     </row>
@@ -1659,25 +1719,25 @@
       <c r="B16" s="7">
         <v>46048</v>
       </c>
-      <c r="C16" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D16" s="51">
+      <c r="C16" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D16" s="16">
         <v>136417443</v>
       </c>
       <c r="E16" s="15">
         <v>3450230509</v>
       </c>
-      <c r="F16" s="47" t="s">
+      <c r="F16" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="G16" s="48" t="s">
+      <c r="G16" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="H16" s="30" t="s">
+      <c r="H16" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="I16" s="29">
+      <c r="I16" s="25">
         <v>46048</v>
       </c>
     </row>
@@ -1688,25 +1748,25 @@
       <c r="B17" s="7">
         <v>46048</v>
       </c>
-      <c r="C17" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D17" s="51">
+      <c r="C17" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D17" s="16">
         <v>136412644</v>
       </c>
       <c r="E17" s="15">
         <v>3450230070</v>
       </c>
-      <c r="F17" s="47" t="s">
+      <c r="F17" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="G17" s="48" t="s">
+      <c r="G17" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="H17" s="30" t="s">
+      <c r="H17" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="I17" s="29">
+      <c r="I17" s="25">
         <v>46048</v>
       </c>
     </row>
@@ -1717,25 +1777,25 @@
       <c r="B18" s="7">
         <v>46048</v>
       </c>
-      <c r="C18" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D18" s="51">
+      <c r="C18" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D18" s="16">
         <v>136418080</v>
       </c>
       <c r="E18" s="15">
         <v>3450230510</v>
       </c>
-      <c r="F18" s="47" t="s">
+      <c r="F18" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="G18" s="48" t="s">
+      <c r="G18" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="H18" s="30" t="s">
+      <c r="H18" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="I18" s="29">
+      <c r="I18" s="25">
         <v>46048</v>
       </c>
     </row>
@@ -1746,25 +1806,25 @@
       <c r="B19" s="7">
         <v>46043</v>
       </c>
-      <c r="C19" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D19" s="51">
+      <c r="C19" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D19" s="16">
         <v>136421044</v>
       </c>
       <c r="E19" s="15">
         <v>3450224305</v>
       </c>
-      <c r="F19" s="47" t="s">
+      <c r="F19" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="G19" s="48" t="s">
+      <c r="G19" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="H19" s="30" t="s">
+      <c r="H19" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="I19" s="29">
+      <c r="I19" s="25">
         <v>46052</v>
       </c>
     </row>
@@ -1775,25 +1835,25 @@
       <c r="B20" s="7">
         <v>46048</v>
       </c>
-      <c r="C20" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D20" s="51">
+      <c r="C20" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D20" s="16">
         <v>136423215</v>
       </c>
       <c r="E20" s="15">
         <v>3450229662</v>
       </c>
-      <c r="F20" s="47" t="s">
+      <c r="F20" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="G20" s="48" t="s">
+      <c r="G20" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="H20" s="30" t="s">
+      <c r="H20" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="I20" s="29">
+      <c r="I20" s="25">
         <v>46048</v>
       </c>
     </row>
@@ -1804,25 +1864,25 @@
       <c r="B21" s="7">
         <v>46048</v>
       </c>
-      <c r="C21" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D21" s="51">
+      <c r="C21" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D21" s="16">
         <v>136409038</v>
       </c>
       <c r="E21" s="15">
         <v>3450229816</v>
       </c>
-      <c r="F21" s="47" t="s">
+      <c r="F21" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="G21" s="48" t="s">
+      <c r="G21" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="H21" s="30" t="s">
+      <c r="H21" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="I21" s="29">
+      <c r="I21" s="25">
         <v>46048</v>
       </c>
     </row>
@@ -1833,25 +1893,25 @@
       <c r="B22" s="7">
         <v>46049</v>
       </c>
-      <c r="C22" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D22" s="51">
+      <c r="C22" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D22" s="16">
         <v>136428646</v>
       </c>
       <c r="E22" s="15">
         <v>3450231257</v>
       </c>
-      <c r="F22" s="47" t="s">
+      <c r="F22" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="G22" s="48" t="s">
+      <c r="G22" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="H22" s="52" t="s">
+      <c r="H22" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="I22" s="29">
+      <c r="I22" s="25">
         <v>46051</v>
       </c>
     </row>
@@ -1862,25 +1922,25 @@
       <c r="B23" s="7">
         <v>46049</v>
       </c>
-      <c r="C23" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D23" s="51">
+      <c r="C23" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D23" s="16">
         <v>136434737</v>
       </c>
       <c r="E23" s="15">
         <v>3450231862</v>
       </c>
-      <c r="F23" s="47" t="s">
+      <c r="F23" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="G23" s="48" t="s">
+      <c r="G23" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="H23" s="30" t="s">
+      <c r="H23" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="I23" s="29">
+      <c r="I23" s="25">
         <v>46049</v>
       </c>
     </row>
@@ -1891,25 +1951,25 @@
       <c r="B24" s="7">
         <v>46049</v>
       </c>
-      <c r="C24" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D24" s="51">
+      <c r="C24" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D24" s="16">
         <v>136433092</v>
       </c>
       <c r="E24" s="15">
         <v>3450231642</v>
       </c>
-      <c r="F24" s="47" t="s">
+      <c r="F24" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="G24" s="48" t="s">
+      <c r="G24" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="H24" s="30" t="s">
+      <c r="H24" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="I24" s="29">
+      <c r="I24" s="25">
         <v>46049</v>
       </c>
     </row>
@@ -1920,25 +1980,25 @@
       <c r="B25" s="7">
         <v>46048</v>
       </c>
-      <c r="C25" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D25" s="51">
+      <c r="C25" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D25" s="16">
         <v>136419463</v>
       </c>
       <c r="E25" s="15">
         <v>3450230531</v>
       </c>
-      <c r="F25" s="47" t="s">
+      <c r="F25" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="G25" s="48" t="s">
+      <c r="G25" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="H25" s="30" t="s">
+      <c r="H25" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="I25" s="29">
+      <c r="I25" s="25">
         <v>46048</v>
       </c>
     </row>
@@ -1949,25 +2009,25 @@
       <c r="B26" s="7">
         <v>46051</v>
       </c>
-      <c r="C26" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D26" s="51">
+      <c r="C26" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D26" s="16">
         <v>136435149</v>
       </c>
       <c r="E26" s="15">
         <v>3450231895</v>
       </c>
-      <c r="F26" s="47" t="s">
+      <c r="F26" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="G26" s="48" t="s">
+      <c r="G26" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="H26" s="30" t="s">
+      <c r="H26" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="I26" s="29">
+      <c r="I26" s="25">
         <v>46052</v>
       </c>
     </row>
@@ -1978,25 +2038,25 @@
       <c r="B27" s="7">
         <v>46050</v>
       </c>
-      <c r="C27" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D27" s="51">
+      <c r="C27" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D27" s="16">
         <v>136451384</v>
       </c>
       <c r="E27" s="15">
         <v>3450233094</v>
       </c>
-      <c r="F27" s="47" t="s">
+      <c r="F27" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="G27" s="48" t="s">
+      <c r="G27" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="H27" s="30" t="s">
+      <c r="H27" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="I27" s="29">
+      <c r="I27" s="25">
         <v>46050</v>
       </c>
     </row>
@@ -2007,25 +2067,25 @@
       <c r="B28" s="7">
         <v>46050</v>
       </c>
-      <c r="C28" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D28" s="51">
+      <c r="C28" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D28" s="16">
         <v>136454769</v>
       </c>
       <c r="E28" s="15">
         <v>3450233413</v>
       </c>
-      <c r="F28" s="47" t="s">
+      <c r="F28" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="G28" s="48" t="s">
+      <c r="G28" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="H28" s="30" t="s">
+      <c r="H28" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="I28" s="29">
+      <c r="I28" s="25">
         <v>46050</v>
       </c>
     </row>
@@ -2036,25 +2096,25 @@
       <c r="B29" s="7">
         <v>46050</v>
       </c>
-      <c r="C29" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D29" s="51">
+      <c r="C29" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D29" s="16">
         <v>136454829</v>
       </c>
       <c r="E29" s="15">
         <v>3450233435</v>
       </c>
-      <c r="F29" s="47" t="s">
+      <c r="F29" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="G29" s="48" t="s">
+      <c r="G29" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="H29" s="30" t="s">
+      <c r="H29" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="I29" s="29">
+      <c r="I29" s="25">
         <v>46050</v>
       </c>
     </row>
@@ -2065,25 +2125,25 @@
       <c r="B30" s="7">
         <v>46044</v>
       </c>
-      <c r="C30" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D30" s="51">
+      <c r="C30" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D30" s="16">
         <v>136367058</v>
       </c>
       <c r="E30" s="15">
         <v>3450226329</v>
       </c>
-      <c r="F30" s="47" t="s">
+      <c r="F30" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="G30" s="48" t="s">
+      <c r="G30" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="H30" s="30" t="s">
+      <c r="H30" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="I30" s="29">
+      <c r="I30" s="25">
         <v>46044</v>
       </c>
     </row>
@@ -2094,25 +2154,25 @@
       <c r="B31" s="7">
         <v>46050</v>
       </c>
-      <c r="C31" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D31" s="51">
+      <c r="C31" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D31" s="16">
         <v>136450018</v>
       </c>
       <c r="E31" s="15">
         <v>3450232995</v>
       </c>
-      <c r="F31" s="47" t="s">
+      <c r="F31" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="G31" s="48" t="s">
+      <c r="G31" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="H31" s="30" t="s">
+      <c r="H31" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="I31" s="29">
+      <c r="I31" s="25">
         <v>46050</v>
       </c>
     </row>
@@ -2123,25 +2183,25 @@
       <c r="B32" s="7">
         <v>46051</v>
       </c>
-      <c r="C32" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D32" s="51">
+      <c r="C32" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D32" s="16">
         <v>136473263</v>
       </c>
       <c r="E32" s="15">
         <v>3450234711</v>
       </c>
-      <c r="F32" s="47" t="s">
+      <c r="F32" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="G32" s="48" t="s">
+      <c r="G32" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="H32" s="30" t="s">
+      <c r="H32" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="I32" s="29">
+      <c r="I32" s="25">
         <v>46051</v>
       </c>
     </row>
@@ -2152,25 +2212,25 @@
       <c r="B33" s="7">
         <v>46051</v>
       </c>
-      <c r="C33" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D33" s="51">
+      <c r="C33" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D33" s="16">
         <v>136461060</v>
       </c>
       <c r="E33" s="15">
         <v>3450233688</v>
       </c>
-      <c r="F33" s="47" t="s">
+      <c r="F33" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="G33" s="48" t="s">
+      <c r="G33" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="H33" s="30" t="s">
+      <c r="H33" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="I33" s="29">
+      <c r="I33" s="25">
         <v>46052</v>
       </c>
     </row>
@@ -2181,25 +2241,25 @@
       <c r="B34" s="7">
         <v>46049</v>
       </c>
-      <c r="C34" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D34" s="51">
+      <c r="C34" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D34" s="16">
         <v>136435757</v>
       </c>
       <c r="E34" s="15">
         <v>3450231940</v>
       </c>
-      <c r="F34" s="47" t="s">
+      <c r="F34" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G34" s="48" t="s">
+      <c r="G34" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="H34" s="30" t="s">
+      <c r="H34" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="I34" s="29">
+      <c r="I34" s="25">
         <v>46049</v>
       </c>
     </row>
@@ -2210,25 +2270,25 @@
       <c r="B35" s="7">
         <v>46046</v>
       </c>
-      <c r="C35" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D35" s="51">
+      <c r="C35" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D35" s="16">
         <v>136312193</v>
       </c>
       <c r="E35" s="15">
         <v>3450222479</v>
       </c>
-      <c r="F35" s="47" t="s">
+      <c r="F35" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="G35" s="48" t="s">
+      <c r="G35" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="H35" s="52" t="s">
+      <c r="H35" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="I35" s="29">
+      <c r="I35" s="25">
         <v>46052</v>
       </c>
     </row>
@@ -2239,25 +2299,25 @@
       <c r="B36" s="7">
         <v>46042</v>
       </c>
-      <c r="C36" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D36" s="51">
+      <c r="C36" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D36" s="16">
         <v>136346822</v>
       </c>
       <c r="E36" s="15">
         <v>3450223250</v>
       </c>
-      <c r="F36" s="47" t="s">
+      <c r="F36" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="G36" s="48" t="s">
+      <c r="G36" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="H36" s="30" t="s">
+      <c r="H36" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="I36" s="29">
+      <c r="I36" s="25">
         <v>46042</v>
       </c>
     </row>
@@ -2268,25 +2328,25 @@
       <c r="B37" s="7">
         <v>46043</v>
       </c>
-      <c r="C37" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D37" s="51">
+      <c r="C37" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D37" s="16">
         <v>136343176</v>
       </c>
       <c r="E37" s="15">
         <v>3450224459</v>
       </c>
-      <c r="F37" s="47" t="s">
+      <c r="F37" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="G37" s="48" t="s">
+      <c r="G37" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="H37" s="30" t="s">
+      <c r="H37" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="I37" s="29">
+      <c r="I37" s="25">
         <v>46052</v>
       </c>
     </row>
@@ -2297,25 +2357,25 @@
       <c r="B38" s="7">
         <v>46043</v>
       </c>
-      <c r="C38" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D38" s="51">
+      <c r="C38" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D38" s="16">
         <v>136350465</v>
       </c>
       <c r="E38" s="15">
         <v>3450225064</v>
       </c>
-      <c r="F38" s="47" t="s">
+      <c r="F38" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="G38" s="48" t="s">
+      <c r="G38" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="H38" s="52" t="s">
+      <c r="H38" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="I38" s="29">
+      <c r="I38" s="25">
         <v>46049</v>
       </c>
     </row>
@@ -2326,25 +2386,25 @@
       <c r="B39" s="7">
         <v>46043</v>
       </c>
-      <c r="C39" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D39" s="51">
+      <c r="C39" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D39" s="16">
         <v>136354505</v>
       </c>
       <c r="E39" s="15">
         <v>3450225471</v>
       </c>
-      <c r="F39" s="47" t="s">
+      <c r="F39" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="G39" s="48" t="s">
+      <c r="G39" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="H39" s="52" t="s">
+      <c r="H39" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="I39" s="29">
+      <c r="I39" s="25">
         <v>46048</v>
       </c>
     </row>
@@ -2355,25 +2415,25 @@
       <c r="B40" s="7">
         <v>46042</v>
       </c>
-      <c r="C40" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D40" s="51">
+      <c r="C40" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D40" s="16">
         <v>136347113</v>
       </c>
       <c r="E40" s="15">
         <v>3450223161</v>
       </c>
-      <c r="F40" s="47" t="s">
+      <c r="F40" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="G40" s="48" t="s">
+      <c r="G40" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="H40" s="30" t="s">
+      <c r="H40" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="I40" s="29">
+      <c r="I40" s="25">
         <v>46042</v>
       </c>
     </row>
@@ -2384,25 +2444,25 @@
       <c r="B41" s="7">
         <v>46043</v>
       </c>
-      <c r="C41" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D41" s="51">
+      <c r="C41" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D41" s="16">
         <v>136342932</v>
       </c>
       <c r="E41" s="15">
         <v>3450224426</v>
       </c>
-      <c r="F41" s="47" t="s">
+      <c r="F41" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="G41" s="48" t="s">
+      <c r="G41" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="H41" s="30" t="s">
+      <c r="H41" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="I41" s="29">
+      <c r="I41" s="25">
         <v>46043</v>
       </c>
     </row>
@@ -2413,25 +2473,25 @@
       <c r="B42" s="7">
         <v>46043</v>
       </c>
-      <c r="C42" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D42" s="51">
+      <c r="C42" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D42" s="16">
         <v>136344343</v>
       </c>
       <c r="E42" s="15">
         <v>3450224514</v>
       </c>
-      <c r="F42" s="47" t="s">
+      <c r="F42" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="G42" s="48" t="s">
+      <c r="G42" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="H42" s="30" t="s">
+      <c r="H42" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="I42" s="29">
+      <c r="I42" s="25">
         <v>46048</v>
       </c>
     </row>
@@ -2442,25 +2502,25 @@
       <c r="B43" s="7">
         <v>46042</v>
       </c>
-      <c r="C43" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D43" s="51">
+      <c r="C43" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D43" s="16">
         <v>136345928</v>
       </c>
       <c r="E43" s="15">
         <v>3450223436</v>
       </c>
-      <c r="F43" s="47" t="s">
+      <c r="F43" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="G43" s="48" t="s">
+      <c r="G43" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="H43" s="30" t="s">
+      <c r="H43" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="I43" s="29">
+      <c r="I43" s="25">
         <v>46042</v>
       </c>
     </row>
@@ -2471,25 +2531,25 @@
       <c r="B44" s="7">
         <v>46043</v>
       </c>
-      <c r="C44" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D44" s="51">
+      <c r="C44" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D44" s="16">
         <v>136345973</v>
       </c>
       <c r="E44" s="15">
         <v>3450224635</v>
       </c>
-      <c r="F44" s="47" t="s">
+      <c r="F44" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="G44" s="48" t="s">
+      <c r="G44" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="H44" s="52" t="s">
+      <c r="H44" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="I44" s="29">
+      <c r="I44" s="25">
         <v>46050</v>
       </c>
     </row>
@@ -2500,25 +2560,25 @@
       <c r="B45" s="7">
         <v>46043</v>
       </c>
-      <c r="C45" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D45" s="51">
+      <c r="C45" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D45" s="16">
         <v>136347211</v>
       </c>
       <c r="E45" s="15">
         <v>3450224789</v>
       </c>
-      <c r="F45" s="47" t="s">
+      <c r="F45" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="G45" s="48" t="s">
+      <c r="G45" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="H45" s="30" t="s">
+      <c r="H45" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="I45" s="29">
+      <c r="I45" s="25">
         <v>46043</v>
       </c>
     </row>
@@ -2529,25 +2589,25 @@
       <c r="B46" s="7">
         <v>46053</v>
       </c>
-      <c r="C46" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D46" s="51">
+      <c r="C46" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D46" s="16">
         <v>136347384</v>
       </c>
       <c r="E46" s="15">
         <v>3450224822</v>
       </c>
-      <c r="F46" s="47" t="s">
+      <c r="F46" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="G46" s="48" t="s">
+      <c r="G46" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="H46" s="52" t="s">
+      <c r="H46" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="I46" s="29">
+      <c r="I46" s="25">
         <v>46048</v>
       </c>
     </row>
@@ -2558,25 +2618,25 @@
       <c r="B47" s="7">
         <v>46048</v>
       </c>
-      <c r="C47" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D47" s="51">
+      <c r="C47" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D47" s="16">
         <v>136408355</v>
       </c>
       <c r="E47" s="15">
         <v>3450229740</v>
       </c>
-      <c r="F47" s="47" t="s">
+      <c r="F47" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="G47" s="48" t="s">
+      <c r="G47" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="H47" s="30" t="s">
+      <c r="H47" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="I47" s="29">
+      <c r="I47" s="25">
         <v>46048</v>
       </c>
     </row>
@@ -2587,25 +2647,25 @@
       <c r="B48" s="7">
         <v>46048</v>
       </c>
-      <c r="C48" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D48" s="51">
+      <c r="C48" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D48" s="16">
         <v>136409179</v>
       </c>
       <c r="E48" s="15">
         <v>3450229849</v>
       </c>
-      <c r="F48" s="47" t="s">
+      <c r="F48" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="G48" s="48" t="s">
+      <c r="G48" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="H48" s="30" t="s">
+      <c r="H48" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="I48" s="29">
+      <c r="I48" s="25">
         <v>46048</v>
       </c>
     </row>
@@ -2616,25 +2676,25 @@
       <c r="B49" s="7">
         <v>46048</v>
       </c>
-      <c r="C49" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D49" s="51">
+      <c r="C49" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D49" s="16">
         <v>136411515</v>
       </c>
       <c r="E49" s="15">
         <v>3450229970</v>
       </c>
-      <c r="F49" s="47" t="s">
+      <c r="F49" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="G49" s="48" t="s">
+      <c r="G49" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="H49" s="30" t="s">
+      <c r="H49" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="I49" s="29">
+      <c r="I49" s="25">
         <v>46048</v>
       </c>
     </row>
@@ -2645,25 +2705,25 @@
       <c r="B50" s="7">
         <v>46044</v>
       </c>
-      <c r="C50" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D50" s="51">
+      <c r="C50" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D50" s="16">
         <v>136374266</v>
       </c>
-      <c r="E50" s="53" t="s">
+      <c r="E50" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="F50" s="47" t="s">
+      <c r="F50" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="G50" s="48" t="s">
+      <c r="G50" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="H50" s="30" t="s">
+      <c r="H50" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="I50" s="29">
+      <c r="I50" s="25">
         <v>46052</v>
       </c>
     </row>
@@ -2674,25 +2734,25 @@
       <c r="B51" s="7">
         <v>46049</v>
       </c>
-      <c r="C51" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D51" s="51">
+      <c r="C51" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D51" s="16">
         <v>136434676</v>
       </c>
       <c r="E51" s="15">
         <v>3450231830</v>
       </c>
-      <c r="F51" s="47" t="s">
+      <c r="F51" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="G51" s="48" t="s">
+      <c r="G51" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="H51" s="30" t="s">
+      <c r="H51" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="I51" s="29">
+      <c r="I51" s="25">
         <v>46049</v>
       </c>
     </row>
@@ -2703,25 +2763,25 @@
       <c r="B52" s="7">
         <v>46049</v>
       </c>
-      <c r="C52" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D52" s="51">
+      <c r="C52" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D52" s="16">
         <v>136426209</v>
       </c>
       <c r="E52" s="15">
         <v>3450231004</v>
       </c>
-      <c r="F52" s="47" t="s">
+      <c r="F52" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="G52" s="48" t="s">
+      <c r="G52" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="H52" s="30" t="s">
+      <c r="H52" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="I52" s="29">
+      <c r="I52" s="25">
         <v>46049</v>
       </c>
     </row>
@@ -2732,25 +2792,25 @@
       <c r="B53" s="7">
         <v>46049</v>
       </c>
-      <c r="C53" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D53" s="51">
+      <c r="C53" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D53" s="16">
         <v>136420826</v>
       </c>
       <c r="E53" s="15">
         <v>3450230620</v>
       </c>
-      <c r="F53" s="47" t="s">
+      <c r="F53" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="G53" s="48" t="s">
+      <c r="G53" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="H53" s="30" t="s">
+      <c r="H53" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="I53" s="29">
+      <c r="I53" s="25">
         <v>46049</v>
       </c>
     </row>
@@ -2761,25 +2821,25 @@
       <c r="B54" s="7">
         <v>46049</v>
       </c>
-      <c r="C54" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D54" s="51">
+      <c r="C54" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D54" s="16">
         <v>136429445</v>
       </c>
       <c r="E54" s="15">
         <v>3450231301</v>
       </c>
-      <c r="F54" s="47" t="s">
+      <c r="F54" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="G54" s="48" t="s">
+      <c r="G54" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="H54" s="30" t="s">
+      <c r="H54" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="I54" s="29">
+      <c r="I54" s="25">
         <v>46049</v>
       </c>
     </row>
@@ -2790,25 +2850,25 @@
       <c r="B55" s="7">
         <v>46073</v>
       </c>
-      <c r="C55" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D55" s="51">
+      <c r="C55" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D55" s="16">
         <v>136355425</v>
       </c>
       <c r="E55" s="15">
         <v>3450225581</v>
       </c>
-      <c r="F55" s="47" t="s">
+      <c r="F55" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="G55" s="48" t="s">
+      <c r="G55" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="H55" s="30" t="s">
+      <c r="H55" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="I55" s="29">
+      <c r="I55" s="25">
         <v>46048</v>
       </c>
     </row>
@@ -2819,25 +2879,25 @@
       <c r="B56" s="7">
         <v>46043</v>
       </c>
-      <c r="C56" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D56" s="51">
+      <c r="C56" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D56" s="16">
         <v>136359741</v>
       </c>
       <c r="E56" s="15">
         <v>3450225108</v>
       </c>
-      <c r="F56" s="47" t="s">
+      <c r="F56" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="G56" s="48" t="s">
+      <c r="G56" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="H56" s="31" t="s">
+      <c r="H56" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="I56" s="29">
+      <c r="I56" s="25">
         <v>46043</v>
       </c>
     </row>
@@ -2848,25 +2908,25 @@
       <c r="B57" s="7">
         <v>46044</v>
       </c>
-      <c r="C57" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D57" s="51">
+      <c r="C57" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D57" s="16">
         <v>136361578</v>
       </c>
       <c r="E57" s="15">
         <v>3450225878</v>
       </c>
-      <c r="F57" s="47" t="s">
+      <c r="F57" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="G57" s="48" t="s">
+      <c r="G57" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="H57" s="31" t="s">
+      <c r="H57" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="I57" s="29">
+      <c r="I57" s="25">
         <v>46044</v>
       </c>
     </row>
@@ -2877,25 +2937,25 @@
       <c r="B58" s="7">
         <v>46044</v>
       </c>
-      <c r="C58" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D58" s="51">
+      <c r="C58" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D58" s="16">
         <v>136364056</v>
       </c>
       <c r="E58" s="15">
         <v>3450226054</v>
       </c>
-      <c r="F58" s="47" t="s">
+      <c r="F58" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="G58" s="48" t="s">
+      <c r="G58" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="H58" s="30" t="s">
+      <c r="H58" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="I58" s="29">
+      <c r="I58" s="25">
         <v>46044</v>
       </c>
     </row>
@@ -2906,25 +2966,25 @@
       <c r="B59" s="7">
         <v>46044</v>
       </c>
-      <c r="C59" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D59" s="51">
+      <c r="C59" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D59" s="16">
         <v>136372291</v>
       </c>
       <c r="E59" s="15">
         <v>3450226846</v>
       </c>
-      <c r="F59" s="47" t="s">
+      <c r="F59" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="G59" s="48" t="s">
+      <c r="G59" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="H59" s="52" t="s">
+      <c r="H59" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="I59" s="29">
+      <c r="I59" s="25">
         <v>46048</v>
       </c>
     </row>
@@ -2935,25 +2995,25 @@
       <c r="B60" s="7">
         <v>46073</v>
       </c>
-      <c r="C60" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D60" s="51">
+      <c r="C60" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D60" s="16">
         <v>136370085</v>
       </c>
       <c r="E60" s="15">
         <v>3450226571</v>
       </c>
-      <c r="F60" s="47" t="s">
+      <c r="F60" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="G60" s="48" t="s">
+      <c r="G60" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="H60" s="30" t="s">
+      <c r="H60" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="I60" s="29">
+      <c r="I60" s="25">
         <v>46048</v>
       </c>
     </row>
@@ -2964,25 +3024,25 @@
       <c r="B61" s="7">
         <v>46044</v>
       </c>
-      <c r="C61" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D61" s="51">
+      <c r="C61" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D61" s="16">
         <v>136374261</v>
       </c>
       <c r="E61" s="15">
         <v>3450227011</v>
       </c>
-      <c r="F61" s="47" t="s">
+      <c r="F61" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="G61" s="48" t="s">
+      <c r="G61" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="H61" s="30" t="s">
+      <c r="H61" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="I61" s="29">
+      <c r="I61" s="25">
         <v>46044</v>
       </c>
     </row>
@@ -2993,25 +3053,25 @@
       <c r="B62" s="7">
         <v>46044</v>
       </c>
-      <c r="C62" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D62" s="51">
+      <c r="C62" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D62" s="16">
         <v>136375328</v>
       </c>
       <c r="E62" s="15">
         <v>3450227143</v>
       </c>
-      <c r="F62" s="47" t="s">
+      <c r="F62" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="G62" s="48" t="s">
+      <c r="G62" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="H62" s="30" t="s">
+      <c r="H62" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="I62" s="29">
+      <c r="I62" s="25">
         <v>46044</v>
       </c>
     </row>
@@ -3022,25 +3082,25 @@
       <c r="B63" s="7">
         <v>46045</v>
       </c>
-      <c r="C63" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D63" s="51">
+      <c r="C63" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D63" s="16">
         <v>136401355</v>
       </c>
       <c r="E63" s="15">
         <v>3450228859</v>
       </c>
-      <c r="F63" s="47" t="s">
+      <c r="F63" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="G63" s="48" t="s">
+      <c r="G63" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="H63" s="30" t="s">
+      <c r="H63" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="I63" s="29">
+      <c r="I63" s="25">
         <v>46045</v>
       </c>
     </row>
@@ -3051,25 +3111,25 @@
       <c r="B64" s="7">
         <v>46045</v>
       </c>
-      <c r="C64" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D64" s="51">
+      <c r="C64" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D64" s="16">
         <v>136404356</v>
       </c>
       <c r="E64" s="15">
         <v>3450228551</v>
       </c>
-      <c r="F64" s="47" t="s">
+      <c r="F64" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="G64" s="48" t="s">
+      <c r="G64" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="H64" s="30" t="s">
+      <c r="H64" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="I64" s="29">
+      <c r="I64" s="25">
         <v>46045</v>
       </c>
     </row>
@@ -3080,25 +3140,25 @@
       <c r="B65" s="7">
         <v>46048</v>
       </c>
-      <c r="C65" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D65" s="51">
+      <c r="C65" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D65" s="16">
         <v>136407947</v>
       </c>
       <c r="E65" s="15">
         <v>3450229695</v>
       </c>
-      <c r="F65" s="47" t="s">
+      <c r="F65" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="G65" s="48" t="s">
+      <c r="G65" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="H65" s="30" t="s">
+      <c r="H65" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="I65" s="29">
+      <c r="I65" s="25">
         <v>46048</v>
       </c>
     </row>
@@ -3109,25 +3169,25 @@
       <c r="B66" s="7">
         <v>46048</v>
       </c>
-      <c r="C66" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D66" s="51">
+      <c r="C66" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D66" s="16">
         <v>136409565</v>
       </c>
       <c r="E66" s="15">
         <v>3450229860</v>
       </c>
-      <c r="F66" s="47" t="s">
+      <c r="F66" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="G66" s="48" t="s">
+      <c r="G66" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="H66" s="30" t="s">
+      <c r="H66" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="I66" s="29">
+      <c r="I66" s="25">
         <v>46048</v>
       </c>
     </row>
@@ -3138,25 +3198,25 @@
       <c r="B67" s="7">
         <v>46048</v>
       </c>
-      <c r="C67" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D67" s="51">
+      <c r="C67" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D67" s="16">
         <v>136410644</v>
       </c>
       <c r="E67" s="15">
         <v>3450229915</v>
       </c>
-      <c r="F67" s="47" t="s">
+      <c r="F67" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="G67" s="48" t="s">
+      <c r="G67" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="H67" s="30" t="s">
+      <c r="H67" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="I67" s="29">
+      <c r="I67" s="25">
         <v>46048</v>
       </c>
     </row>
@@ -3167,25 +3227,25 @@
       <c r="B68" s="7">
         <v>46049</v>
       </c>
-      <c r="C68" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D68" s="51">
+      <c r="C68" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D68" s="16">
         <v>136426683</v>
       </c>
       <c r="E68" s="15">
         <v>3450231081</v>
       </c>
-      <c r="F68" s="47" t="s">
+      <c r="F68" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="G68" s="48" t="s">
+      <c r="G68" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="H68" s="30" t="s">
+      <c r="H68" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="I68" s="29">
+      <c r="I68" s="25">
         <v>46049</v>
       </c>
     </row>
@@ -3196,25 +3256,25 @@
       <c r="B69" s="7">
         <v>46049</v>
       </c>
-      <c r="C69" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D69" s="51">
+      <c r="C69" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D69" s="16">
         <v>136434085</v>
       </c>
       <c r="E69" s="15">
         <v>3450231752</v>
       </c>
-      <c r="F69" s="47" t="s">
+      <c r="F69" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="G69" s="48" t="s">
+      <c r="G69" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="H69" s="30" t="s">
+      <c r="H69" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="I69" s="29">
+      <c r="I69" s="25">
         <v>46049</v>
       </c>
     </row>
@@ -3225,25 +3285,25 @@
       <c r="B70" s="7">
         <v>46048</v>
       </c>
-      <c r="C70" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D70" s="51">
+      <c r="C70" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D70" s="16">
         <v>136414652</v>
       </c>
       <c r="E70" s="15">
         <v>3450230245</v>
       </c>
-      <c r="F70" s="47" t="s">
+      <c r="F70" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="G70" s="48" t="s">
+      <c r="G70" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="H70" s="30" t="s">
+      <c r="H70" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="I70" s="29">
+      <c r="I70" s="25">
         <v>46048</v>
       </c>
     </row>
@@ -3254,25 +3314,25 @@
       <c r="B71" s="7">
         <v>46048</v>
       </c>
-      <c r="C71" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D71" s="51">
+      <c r="C71" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D71" s="16">
         <v>136415341</v>
       </c>
       <c r="E71" s="15">
         <v>3450230333</v>
       </c>
-      <c r="F71" s="47" t="s">
+      <c r="F71" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="G71" s="48" t="s">
+      <c r="G71" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="H71" s="30" t="s">
+      <c r="H71" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="I71" s="29">
+      <c r="I71" s="25">
         <v>46048</v>
       </c>
     </row>
@@ -3283,71 +3343,71 @@
       <c r="B72" s="7">
         <v>46049</v>
       </c>
-      <c r="C72" s="22">
-        <v>46055</v>
-      </c>
-      <c r="D72" s="51">
+      <c r="C72" s="18">
+        <v>46055</v>
+      </c>
+      <c r="D72" s="16">
         <v>136427242</v>
       </c>
       <c r="E72" s="15">
         <v>3450231180</v>
       </c>
-      <c r="F72" s="47" t="s">
+      <c r="F72" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="G72" s="48" t="s">
+      <c r="G72" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="H72" s="30" t="s">
+      <c r="H72" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="I72" s="29">
+      <c r="I72" s="25">
         <v>46049</v>
       </c>
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="6"/>
       <c r="B73" s="7"/>
-      <c r="C73" s="22"/>
-      <c r="D73" s="50"/>
-      <c r="E73" s="34"/>
-      <c r="F73" s="26"/>
-      <c r="G73" s="27"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="38"/>
+      <c r="E73" s="29"/>
+      <c r="F73" s="22"/>
+      <c r="G73" s="23"/>
       <c r="H73" s="11"/>
-      <c r="I73" s="29"/>
+      <c r="I73" s="25"/>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="6"/>
       <c r="B74" s="7"/>
-      <c r="C74" s="22"/>
-      <c r="D74" s="28"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="24"/>
       <c r="E74" s="15"/>
       <c r="F74" s="10"/>
-      <c r="G74" s="27"/>
+      <c r="G74" s="23"/>
       <c r="H74" s="11"/>
-      <c r="I74" s="29"/>
+      <c r="I74" s="25"/>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="6"/>
       <c r="B75" s="7"/>
-      <c r="C75" s="22"/>
-      <c r="D75" s="28"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="24"/>
       <c r="E75" s="15"/>
       <c r="F75" s="10"/>
-      <c r="G75" s="27"/>
+      <c r="G75" s="23"/>
       <c r="H75" s="11"/>
-      <c r="I75" s="29"/>
+      <c r="I75" s="25"/>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="6"/>
       <c r="B76" s="7"/>
-      <c r="C76" s="22"/>
-      <c r="D76" s="28"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="24"/>
       <c r="E76" s="15"/>
       <c r="F76" s="10"/>
-      <c r="G76" s="27"/>
+      <c r="G76" s="23"/>
       <c r="H76" s="11"/>
-      <c r="I76" s="29"/>
+      <c r="I76" s="25"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -3369,17 +3429,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD26F43-5C8A-4C67-93F6-3B4E17ED8491}">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="15.85546875" style="14" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" style="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" style="14" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" style="14" customWidth="1"/>
+    <col min="4" max="4" width="26" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.5703125" style="14" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30.140625" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.5703125" customWidth="1"/>
-    <col min="9" max="9" width="21" style="21" customWidth="1"/>
+    <col min="9" max="9" width="21" style="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -3407,7 +3468,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="21" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3415,472 +3476,781 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="29"/>
+      <c r="B2" s="30">
+        <v>46045</v>
+      </c>
+      <c r="C2" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D2" s="16">
+        <v>136393265</v>
+      </c>
+      <c r="E2" s="41">
+        <v>3450228562</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="I2" s="25">
+        <v>46045</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="29"/>
+      <c r="B3" s="30">
+        <v>46045</v>
+      </c>
+      <c r="C3" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D3" s="16">
+        <v>136382428</v>
+      </c>
+      <c r="E3" s="41">
+        <v>3450227430</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="I3" s="25">
+        <v>46045</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="29"/>
+      <c r="B4" s="30">
+        <v>46050</v>
+      </c>
+      <c r="C4" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D4" s="16">
+        <v>136442657</v>
+      </c>
+      <c r="E4" s="42">
+        <v>3450232269</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I4" s="25">
+        <v>46050</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="32"/>
+      <c r="B5" s="30">
+        <v>46050</v>
+      </c>
+      <c r="C5" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D5" s="16">
+        <v>136445906</v>
+      </c>
+      <c r="E5" s="41">
+        <v>3450232544</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="I5" s="25">
+        <v>46050</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="29"/>
+      <c r="B6" s="30">
+        <v>46050</v>
+      </c>
+      <c r="C6" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D6" s="16">
+        <v>136452550</v>
+      </c>
+      <c r="E6" s="41">
+        <v>3450233237</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="I6" s="25">
+        <v>46050</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="29"/>
+      <c r="B7" s="30">
+        <v>46066</v>
+      </c>
+      <c r="C7" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D7" s="16">
+        <v>136465056</v>
+      </c>
+      <c r="E7" s="41">
+        <v>3450232709</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="I7" s="25">
+        <v>46055</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="29"/>
+      <c r="B8" s="30">
+        <v>46051</v>
+      </c>
+      <c r="C8" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D8" s="16">
+        <v>136471630</v>
+      </c>
+      <c r="E8" s="41">
+        <v>3450234557</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="I8" s="25">
+        <v>46055</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="29"/>
+      <c r="B9" s="30">
+        <v>46051</v>
+      </c>
+      <c r="C9" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D9" s="16">
+        <v>136465949</v>
+      </c>
+      <c r="E9" s="41">
+        <v>3450234304</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="G9" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="I9" s="25">
+        <v>46051</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="35"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="29"/>
+      <c r="B10" s="30">
+        <v>46051</v>
+      </c>
+      <c r="C10" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D10" s="16">
+        <v>136468154</v>
+      </c>
+      <c r="E10" s="41">
+        <v>3450234381</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="G10" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" s="25">
+        <v>46051</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="29"/>
+      <c r="B11" s="30">
+        <v>46051</v>
+      </c>
+      <c r="C11" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D11" s="16">
+        <v>136466617</v>
+      </c>
+      <c r="E11" s="41">
+        <v>3450234337</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="G11" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="I11" s="25">
+        <v>46055</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="29"/>
+      <c r="B12" s="30">
+        <v>46051</v>
+      </c>
+      <c r="C12" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D12" s="16">
+        <v>136477003</v>
+      </c>
+      <c r="E12" s="41">
+        <v>3450234227</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="G12" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12" s="25">
+        <v>46051</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="35"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="29"/>
+      <c r="B13" s="30">
+        <v>46073</v>
+      </c>
+      <c r="C13" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D13" s="16">
+        <v>136369261</v>
+      </c>
+      <c r="E13" s="41">
+        <v>3450226527</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="45" t="s">
+        <v>141</v>
+      </c>
+      <c r="I13" s="25">
+        <v>46048</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="29"/>
+      <c r="B14" s="30">
+        <v>46050</v>
+      </c>
+      <c r="C14" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D14" s="16">
+        <v>136440560</v>
+      </c>
+      <c r="E14" s="41">
+        <v>3450232137</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="G14" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="I14" s="25">
+        <v>46050</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="35"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="29"/>
+      <c r="B15" s="30">
+        <v>46045</v>
+      </c>
+      <c r="C15" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D15" s="16">
+        <v>136388552</v>
+      </c>
+      <c r="E15" s="41">
+        <v>3450228034</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="G15" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="I15" s="25">
+        <v>46055</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="29"/>
+      <c r="B16" s="30">
+        <v>46049</v>
+      </c>
+      <c r="C16" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D16" s="16">
+        <v>136440124</v>
+      </c>
+      <c r="E16" s="41">
+        <v>3450231378</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="G16" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="I16" s="25">
+        <v>46055</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="29"/>
+      <c r="B17" s="7">
+        <v>46050</v>
+      </c>
+      <c r="C17" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D17" s="16">
+        <v>136448221</v>
+      </c>
+      <c r="E17" s="41">
+        <v>3450232808</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="G17" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="I17" s="25">
+        <v>46055</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="29"/>
+      <c r="B18" s="7">
+        <v>46050</v>
+      </c>
+      <c r="C18" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D18" s="16">
+        <v>136453096</v>
+      </c>
+      <c r="E18" s="41">
+        <v>3450233281</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="G18" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="I18" s="25">
+        <v>46050</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="29"/>
+      <c r="B19" s="7">
+        <v>46045</v>
+      </c>
+      <c r="C19" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D19" s="16">
+        <v>136382326</v>
+      </c>
+      <c r="E19" s="41">
+        <v>3450227429</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G19" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I19" s="25">
+        <v>46045</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="29"/>
+      <c r="B20" s="7">
+        <v>46045</v>
+      </c>
+      <c r="C20" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D20" s="16">
+        <v>136387100</v>
+      </c>
+      <c r="E20" s="41">
+        <v>3450227880</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="G20" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="I20" s="25">
+        <v>46045</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="29"/>
+      <c r="B21" s="7">
+        <v>46045</v>
+      </c>
+      <c r="C21" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D21" s="16">
+        <v>136388457</v>
+      </c>
+      <c r="E21" s="41">
+        <v>3450228023</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="G21" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I21" s="25">
+        <v>46045</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="29"/>
+      <c r="B22" s="7">
+        <v>46045</v>
+      </c>
+      <c r="C22" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D22" s="16">
+        <v>136390303</v>
+      </c>
+      <c r="E22" s="43">
+        <v>3450228243</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="G22" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I22" s="25">
+        <v>46045</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="13"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>46045</v>
+      </c>
+      <c r="C23" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D23" s="16">
+        <v>136391159</v>
+      </c>
+      <c r="E23" s="41">
+        <v>3450228331</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G23" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I23" s="25">
+        <v>46045</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="9"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>46045</v>
+      </c>
+      <c r="C24" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D24" s="16">
+        <v>136394737</v>
+      </c>
+      <c r="E24" s="41">
+        <v>3450228749</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I24" s="25">
+        <v>46045</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="9"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>46045</v>
+      </c>
+      <c r="C25" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D25" s="16">
+        <v>136395864</v>
+      </c>
+      <c r="E25" s="41">
+        <v>3450228925</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="G25" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I25" s="25">
+        <v>46045</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="9"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>46046</v>
+      </c>
+      <c r="C26" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D26" s="16">
+        <v>136398875</v>
+      </c>
+      <c r="E26" s="41">
+        <v>3450229101</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="G26" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I26" s="25">
+        <v>46046</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="9"/>
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>46046</v>
+      </c>
+      <c r="C27" s="18">
+        <v>46056</v>
+      </c>
+      <c r="D27" s="16">
+        <v>136399912</v>
+      </c>
+      <c r="E27" s="41">
+        <v>3450229167</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="G27" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I27" s="25">
+        <v>46046</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="15"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="44"/>
       <c r="F28" s="10"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="9"/>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="9"/>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="9"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="9"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="6"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="6"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="6"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="6"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="6"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="6"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="25"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="3">
+    <cfRule type="notContainsBlanks" priority="4">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A23:A33" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A28" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G28" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A22" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
-      <formula1>$J$2</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B17" xr:uid="{7AD82A11-4EC7-4EF9-95FB-52EC6839A0E7}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B16" xr:uid="{7AD82A11-4EC7-4EF9-95FB-52EC6839A0E7}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3935,40 +4305,40 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="23"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="8"/>
       <c r="F2" s="10"/>
-      <c r="G2" s="24"/>
+      <c r="G2" s="20"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="21"/>
+      <c r="I2" s="17"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="23"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="19"/>
       <c r="E3" s="8"/>
       <c r="F3" s="10"/>
-      <c r="G3" s="24"/>
+      <c r="G3" s="20"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="21"/>
+      <c r="I3" s="17"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="23"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="19"/>
       <c r="E4" s="8"/>
       <c r="F4" s="10"/>
-      <c r="G4" s="24"/>
+      <c r="G4" s="20"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="21"/>
+      <c r="I4" s="17"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -3976,12 +4346,12 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="23"/>
+      <c r="D5" s="19"/>
       <c r="E5" s="8"/>
       <c r="F5" s="10"/>
-      <c r="G5" s="24"/>
+      <c r="G5" s="20"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="21"/>
+      <c r="I5" s="17"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
@@ -3989,12 +4359,12 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="23"/>
+      <c r="D6" s="19"/>
       <c r="E6" s="8"/>
       <c r="F6" s="10"/>
-      <c r="G6" s="24"/>
+      <c r="G6" s="20"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="21"/>
+      <c r="I6" s="17"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
@@ -4002,12 +4372,12 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="23"/>
+      <c r="D7" s="19"/>
       <c r="E7" s="8"/>
       <c r="F7" s="10"/>
-      <c r="G7" s="24"/>
+      <c r="G7" s="20"/>
       <c r="H7" s="9"/>
-      <c r="I7" s="21"/>
+      <c r="I7" s="17"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
@@ -4015,12 +4385,12 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="23"/>
+      <c r="D8" s="19"/>
       <c r="E8" s="8"/>
       <c r="F8" s="10"/>
-      <c r="G8" s="24"/>
+      <c r="G8" s="20"/>
       <c r="H8" s="9"/>
-      <c r="I8" s="21"/>
+      <c r="I8" s="17"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
@@ -4028,12 +4398,12 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="23"/>
+      <c r="D9" s="19"/>
       <c r="E9" s="8"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="24"/>
+      <c r="G9" s="20"/>
       <c r="H9" s="9"/>
-      <c r="I9" s="21"/>
+      <c r="I9" s="17"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
@@ -4041,12 +4411,12 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="23"/>
+      <c r="D10" s="19"/>
       <c r="E10" s="8"/>
       <c r="F10" s="10"/>
-      <c r="G10" s="24"/>
+      <c r="G10" s="20"/>
       <c r="H10" s="9"/>
-      <c r="I10" s="21"/>
+      <c r="I10" s="17"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
@@ -4054,12 +4424,12 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="23"/>
+      <c r="D11" s="19"/>
       <c r="E11" s="8"/>
       <c r="F11" s="10"/>
-      <c r="G11" s="24"/>
+      <c r="G11" s="20"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="21"/>
+      <c r="I11" s="17"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
@@ -4067,12 +4437,12 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="23"/>
+      <c r="D12" s="19"/>
       <c r="E12" s="8"/>
       <c r="F12" s="10"/>
-      <c r="G12" s="24"/>
+      <c r="G12" s="20"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="21"/>
+      <c r="I12" s="17"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
@@ -4080,12 +4450,12 @@
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="23"/>
+      <c r="D13" s="19"/>
       <c r="E13" s="8"/>
       <c r="F13" s="10"/>
-      <c r="G13" s="24"/>
+      <c r="G13" s="20"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="21"/>
+      <c r="I13" s="17"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
@@ -4093,12 +4463,12 @@
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="23"/>
+      <c r="D14" s="19"/>
       <c r="E14" s="8"/>
       <c r="F14" s="10"/>
-      <c r="G14" s="24"/>
+      <c r="G14" s="20"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="21"/>
+      <c r="I14" s="17"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
@@ -4106,23 +4476,23 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="23"/>
+      <c r="D15" s="19"/>
       <c r="E15" s="8"/>
       <c r="F15" s="10"/>
-      <c r="G15" s="24"/>
+      <c r="G15" s="20"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="21"/>
+      <c r="I15" s="17"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="23"/>
+      <c r="D16" s="19"/>
       <c r="E16" s="8"/>
       <c r="F16" s="10"/>
-      <c r="G16" s="24"/>
+      <c r="G16" s="20"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="21"/>
+      <c r="I16" s="17"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6"/>
@@ -4133,7 +4503,7 @@
       <c r="F17" s="10"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="21"/>
+      <c r="I17" s="17"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>
@@ -4144,7 +4514,7 @@
       <c r="F18" s="10"/>
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="21"/>
+      <c r="I18" s="17"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
@@ -4155,7 +4525,7 @@
       <c r="F19" s="11"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="21"/>
+      <c r="I19" s="17"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -4166,7 +4536,7 @@
       <c r="F20" s="13"/>
       <c r="G20" s="6"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="21"/>
+      <c r="I20" s="17"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -4354,10 +4724,10 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="45" t="s">
+      <c r="H1" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="28" t="s">
         <v>8</v>
       </c>
     </row>
@@ -4365,40 +4735,40 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="23"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="8"/>
       <c r="F2" s="10"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="29"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="25"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="23"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="19"/>
       <c r="E3" s="8"/>
       <c r="F3" s="10"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="29"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="23"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="19"/>
       <c r="E4" s="8"/>
       <c r="F4" s="10"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="29"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -4406,12 +4776,12 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="23"/>
+      <c r="D5" s="19"/>
       <c r="E5" s="8"/>
       <c r="F5" s="10"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="29"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
@@ -4419,12 +4789,12 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="23"/>
+      <c r="D6" s="19"/>
       <c r="E6" s="8"/>
       <c r="F6" s="10"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="29"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
@@ -4432,12 +4802,12 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="23"/>
+      <c r="D7" s="19"/>
       <c r="E7" s="8"/>
       <c r="F7" s="10"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="29"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="25"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
@@ -4445,12 +4815,12 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="23"/>
+      <c r="D8" s="19"/>
       <c r="E8" s="8"/>
       <c r="F8" s="10"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="29"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="25"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
@@ -4458,12 +4828,12 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="23"/>
+      <c r="D9" s="19"/>
       <c r="E9" s="8"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="29"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="25"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
@@ -4471,12 +4841,12 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="23"/>
+      <c r="D10" s="19"/>
       <c r="E10" s="8"/>
       <c r="F10" s="10"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="29"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="25"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
@@ -4484,12 +4854,12 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="23"/>
+      <c r="D11" s="19"/>
       <c r="E11" s="8"/>
       <c r="F11" s="10"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="29"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="25"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
@@ -4497,12 +4867,12 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="23"/>
+      <c r="D12" s="19"/>
       <c r="E12" s="8"/>
       <c r="F12" s="10"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="29"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="25"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
@@ -4510,12 +4880,12 @@
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="23"/>
+      <c r="D13" s="19"/>
       <c r="E13" s="8"/>
       <c r="F13" s="10"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="29"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
@@ -4523,12 +4893,12 @@
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="23"/>
+      <c r="D14" s="19"/>
       <c r="E14" s="8"/>
       <c r="F14" s="10"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="29"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="25"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
@@ -4536,23 +4906,23 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="23"/>
+      <c r="D15" s="19"/>
       <c r="E15" s="8"/>
       <c r="F15" s="10"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="29"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="25"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="23"/>
+      <c r="D16" s="19"/>
       <c r="E16" s="8"/>
       <c r="F16" s="10"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="29"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="25"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6"/>
@@ -4562,8 +4932,8 @@
       <c r="E17" s="12"/>
       <c r="F17" s="10"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="29"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="25"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>
@@ -4573,8 +4943,8 @@
       <c r="E18" s="12"/>
       <c r="F18" s="10"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="29"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="25"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
@@ -4584,8 +4954,8 @@
       <c r="E19" s="12"/>
       <c r="F19" s="11"/>
       <c r="G19" s="6"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="29"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="25"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -4595,8 +4965,8 @@
       <c r="E20" s="8"/>
       <c r="F20" s="13"/>
       <c r="G20" s="6"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="29"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="25"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -4606,7 +4976,7 @@
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="46"/>
+      <c r="H21" s="35"/>
       <c r="I21" s="11"/>
     </row>
     <row r="22" spans="1:9">
@@ -4617,7 +4987,7 @@
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="46"/>
+      <c r="H22" s="35"/>
       <c r="I22" s="11"/>
     </row>
     <row r="23" spans="1:9">
@@ -4628,7 +4998,7 @@
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
       <c r="G23" s="6"/>
-      <c r="H23" s="46"/>
+      <c r="H23" s="35"/>
       <c r="I23" s="11"/>
     </row>
     <row r="24" spans="1:9">
@@ -4639,7 +5009,7 @@
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
       <c r="G24" s="6"/>
-      <c r="H24" s="46"/>
+      <c r="H24" s="35"/>
       <c r="I24" s="11"/>
     </row>
     <row r="25" spans="1:9">
@@ -4650,7 +5020,7 @@
       <c r="E25" s="8"/>
       <c r="F25" s="9"/>
       <c r="G25" s="6"/>
-      <c r="H25" s="46"/>
+      <c r="H25" s="35"/>
       <c r="I25" s="11"/>
     </row>
     <row r="26" spans="1:9">
@@ -4661,7 +5031,7 @@
       <c r="E26" s="8"/>
       <c r="F26" s="9"/>
       <c r="G26" s="6"/>
-      <c r="H26" s="46"/>
+      <c r="H26" s="35"/>
       <c r="I26" s="11"/>
     </row>
     <row r="27" spans="1:9">
@@ -4672,7 +5042,7 @@
       <c r="E27" s="8"/>
       <c r="F27" s="9"/>
       <c r="G27" s="6"/>
-      <c r="H27" s="46"/>
+      <c r="H27" s="35"/>
       <c r="I27" s="11"/>
     </row>
     <row r="28" spans="1:9">
@@ -4683,7 +5053,7 @@
       <c r="E28" s="8"/>
       <c r="F28" s="9"/>
       <c r="G28" s="6"/>
-      <c r="H28" s="46"/>
+      <c r="H28" s="35"/>
       <c r="I28" s="11"/>
     </row>
     <row r="29" spans="1:9">
@@ -4694,7 +5064,7 @@
       <c r="E29" s="8"/>
       <c r="F29" s="9"/>
       <c r="G29" s="6"/>
-      <c r="H29" s="46"/>
+      <c r="H29" s="35"/>
       <c r="I29" s="11"/>
     </row>
     <row r="30" spans="1:9">
@@ -4705,7 +5075,7 @@
       <c r="E30" s="8"/>
       <c r="F30" s="9"/>
       <c r="G30" s="6"/>
-      <c r="H30" s="46"/>
+      <c r="H30" s="35"/>
       <c r="I30" s="11"/>
     </row>
     <row r="31" spans="1:9">
@@ -4716,7 +5086,7 @@
       <c r="E31" s="8"/>
       <c r="F31" s="9"/>
       <c r="G31" s="6"/>
-      <c r="H31" s="46"/>
+      <c r="H31" s="35"/>
       <c r="I31" s="11"/>
     </row>
     <row r="32" spans="1:9">
@@ -4727,7 +5097,7 @@
       <c r="E32" s="8"/>
       <c r="F32" s="9"/>
       <c r="G32" s="6"/>
-      <c r="H32" s="46"/>
+      <c r="H32" s="35"/>
       <c r="I32" s="11"/>
     </row>
     <row r="33" spans="1:9">
@@ -4738,7 +5108,7 @@
       <c r="E33" s="8"/>
       <c r="F33" s="9"/>
       <c r="G33" s="6"/>
-      <c r="H33" s="46"/>
+      <c r="H33" s="35"/>
       <c r="I33" s="11"/>
     </row>
   </sheetData>
@@ -4786,10 +5156,10 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="45" t="s">
+      <c r="H1" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="28" t="s">
         <v>8</v>
       </c>
     </row>
@@ -4797,40 +5167,40 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="23"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="8"/>
       <c r="F2" s="10"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="29"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="25"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="23"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="19"/>
       <c r="E3" s="8"/>
       <c r="F3" s="10"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="29"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="23"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="19"/>
       <c r="E4" s="8"/>
       <c r="F4" s="10"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="29"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -4838,12 +5208,12 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="23"/>
+      <c r="D5" s="19"/>
       <c r="E5" s="8"/>
       <c r="F5" s="10"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="29"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
@@ -4851,12 +5221,12 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="23"/>
+      <c r="D6" s="19"/>
       <c r="E6" s="8"/>
       <c r="F6" s="10"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="29"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
@@ -4864,12 +5234,12 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="23"/>
+      <c r="D7" s="19"/>
       <c r="E7" s="8"/>
       <c r="F7" s="10"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="29"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="25"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
@@ -4877,12 +5247,12 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="23"/>
+      <c r="D8" s="19"/>
       <c r="E8" s="8"/>
       <c r="F8" s="10"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="29"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="25"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
@@ -4890,12 +5260,12 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="23"/>
+      <c r="D9" s="19"/>
       <c r="E9" s="8"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="29"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="25"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
@@ -4903,12 +5273,12 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="23"/>
+      <c r="D10" s="19"/>
       <c r="E10" s="8"/>
       <c r="F10" s="10"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="29"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="25"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
@@ -4916,12 +5286,12 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="23"/>
+      <c r="D11" s="19"/>
       <c r="E11" s="8"/>
       <c r="F11" s="10"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="29"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="25"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
@@ -4929,12 +5299,12 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="23"/>
+      <c r="D12" s="19"/>
       <c r="E12" s="8"/>
       <c r="F12" s="10"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="29"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="25"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
@@ -4942,12 +5312,12 @@
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="23"/>
+      <c r="D13" s="19"/>
       <c r="E13" s="8"/>
       <c r="F13" s="10"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="29"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
@@ -4955,12 +5325,12 @@
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="23"/>
+      <c r="D14" s="19"/>
       <c r="E14" s="8"/>
       <c r="F14" s="10"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="29"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="25"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
@@ -4968,23 +5338,23 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="23"/>
+      <c r="D15" s="19"/>
       <c r="E15" s="8"/>
       <c r="F15" s="10"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="29"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="25"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="23"/>
+      <c r="D16" s="19"/>
       <c r="E16" s="8"/>
       <c r="F16" s="10"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="29"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="25"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6"/>
@@ -4994,8 +5364,8 @@
       <c r="E17" s="12"/>
       <c r="F17" s="10"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="29"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="25"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>
@@ -5005,8 +5375,8 @@
       <c r="E18" s="12"/>
       <c r="F18" s="10"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="29"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="25"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
@@ -5016,8 +5386,8 @@
       <c r="E19" s="12"/>
       <c r="F19" s="11"/>
       <c r="G19" s="6"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="29"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="25"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -5027,8 +5397,8 @@
       <c r="E20" s="8"/>
       <c r="F20" s="13"/>
       <c r="G20" s="6"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="29"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="25"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -5038,7 +5408,7 @@
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="46"/>
+      <c r="H21" s="35"/>
       <c r="I21" s="11"/>
     </row>
     <row r="22" spans="1:9">
@@ -5049,7 +5419,7 @@
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="46"/>
+      <c r="H22" s="35"/>
       <c r="I22" s="11"/>
     </row>
     <row r="23" spans="1:9">
@@ -5060,7 +5430,7 @@
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
       <c r="G23" s="6"/>
-      <c r="H23" s="46"/>
+      <c r="H23" s="35"/>
       <c r="I23" s="11"/>
     </row>
     <row r="24" spans="1:9">
@@ -5071,7 +5441,7 @@
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
       <c r="G24" s="6"/>
-      <c r="H24" s="46"/>
+      <c r="H24" s="35"/>
       <c r="I24" s="11"/>
     </row>
     <row r="25" spans="1:9">
@@ -5082,7 +5452,7 @@
       <c r="E25" s="8"/>
       <c r="F25" s="9"/>
       <c r="G25" s="6"/>
-      <c r="H25" s="46"/>
+      <c r="H25" s="35"/>
       <c r="I25" s="11"/>
     </row>
     <row r="26" spans="1:9">
@@ -5093,7 +5463,7 @@
       <c r="E26" s="8"/>
       <c r="F26" s="9"/>
       <c r="G26" s="6"/>
-      <c r="H26" s="46"/>
+      <c r="H26" s="35"/>
       <c r="I26" s="11"/>
     </row>
     <row r="27" spans="1:9">
@@ -5104,7 +5474,7 @@
       <c r="E27" s="8"/>
       <c r="F27" s="9"/>
       <c r="G27" s="6"/>
-      <c r="H27" s="46"/>
+      <c r="H27" s="35"/>
       <c r="I27" s="11"/>
     </row>
     <row r="28" spans="1:9">
@@ -5115,7 +5485,7 @@
       <c r="E28" s="8"/>
       <c r="F28" s="9"/>
       <c r="G28" s="6"/>
-      <c r="H28" s="46"/>
+      <c r="H28" s="35"/>
       <c r="I28" s="11"/>
     </row>
     <row r="29" spans="1:9">
@@ -5126,7 +5496,7 @@
       <c r="E29" s="8"/>
       <c r="F29" s="9"/>
       <c r="G29" s="6"/>
-      <c r="H29" s="46"/>
+      <c r="H29" s="35"/>
       <c r="I29" s="11"/>
     </row>
     <row r="30" spans="1:9">
@@ -5137,7 +5507,7 @@
       <c r="E30" s="8"/>
       <c r="F30" s="9"/>
       <c r="G30" s="6"/>
-      <c r="H30" s="46"/>
+      <c r="H30" s="35"/>
       <c r="I30" s="11"/>
     </row>
     <row r="31" spans="1:9">
@@ -5148,7 +5518,7 @@
       <c r="E31" s="8"/>
       <c r="F31" s="9"/>
       <c r="G31" s="6"/>
-      <c r="H31" s="46"/>
+      <c r="H31" s="35"/>
       <c r="I31" s="11"/>
     </row>
     <row r="32" spans="1:9">
@@ -5159,7 +5529,7 @@
       <c r="E32" s="8"/>
       <c r="F32" s="9"/>
       <c r="G32" s="6"/>
-      <c r="H32" s="46"/>
+      <c r="H32" s="35"/>
       <c r="I32" s="11"/>
     </row>
     <row r="33" spans="1:9">
@@ -5170,7 +5540,7 @@
       <c r="E33" s="8"/>
       <c r="F33" s="9"/>
       <c r="G33" s="6"/>
-      <c r="H33" s="46"/>
+      <c r="H33" s="35"/>
       <c r="I33" s="11"/>
     </row>
   </sheetData>
@@ -5229,10 +5599,10 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="45" t="s">
+      <c r="H1" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="28" t="s">
         <v>8</v>
       </c>
     </row>
@@ -5240,40 +5610,40 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="23"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="8"/>
       <c r="F2" s="10"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="29"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="25"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="23"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="19"/>
       <c r="E3" s="8"/>
       <c r="F3" s="10"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="29"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="23"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="19"/>
       <c r="E4" s="8"/>
       <c r="F4" s="10"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="29"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -5281,12 +5651,12 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="23"/>
+      <c r="D5" s="19"/>
       <c r="E5" s="8"/>
       <c r="F5" s="10"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="29"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
@@ -5294,12 +5664,12 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="23"/>
+      <c r="D6" s="19"/>
       <c r="E6" s="8"/>
       <c r="F6" s="10"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="29"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
@@ -5307,12 +5677,12 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="23"/>
+      <c r="D7" s="19"/>
       <c r="E7" s="8"/>
       <c r="F7" s="10"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="29"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="25"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
@@ -5320,12 +5690,12 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="23"/>
+      <c r="D8" s="19"/>
       <c r="E8" s="8"/>
       <c r="F8" s="10"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="29"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="25"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
@@ -5333,12 +5703,12 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="23"/>
+      <c r="D9" s="19"/>
       <c r="E9" s="8"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="29"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="25"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
@@ -5346,12 +5716,12 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="23"/>
+      <c r="D10" s="19"/>
       <c r="E10" s="8"/>
       <c r="F10" s="10"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="29"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="25"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
@@ -5359,12 +5729,12 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="23"/>
+      <c r="D11" s="19"/>
       <c r="E11" s="8"/>
       <c r="F11" s="10"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="29"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="25"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
@@ -5372,12 +5742,12 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="23"/>
+      <c r="D12" s="19"/>
       <c r="E12" s="8"/>
       <c r="F12" s="10"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="29"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="25"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
@@ -5385,12 +5755,12 @@
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="23"/>
+      <c r="D13" s="19"/>
       <c r="E13" s="8"/>
       <c r="F13" s="10"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="29"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
@@ -5398,12 +5768,12 @@
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="23"/>
+      <c r="D14" s="19"/>
       <c r="E14" s="8"/>
       <c r="F14" s="10"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="29"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="25"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
@@ -5411,23 +5781,23 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="23"/>
+      <c r="D15" s="19"/>
       <c r="E15" s="8"/>
       <c r="F15" s="10"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="29"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="25"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="23"/>
+      <c r="D16" s="19"/>
       <c r="E16" s="8"/>
       <c r="F16" s="10"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="29"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="25"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6"/>
@@ -5437,8 +5807,8 @@
       <c r="E17" s="12"/>
       <c r="F17" s="10"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="29"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="25"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>
@@ -5448,8 +5818,8 @@
       <c r="E18" s="12"/>
       <c r="F18" s="10"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="29"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="25"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
@@ -5459,8 +5829,8 @@
       <c r="E19" s="12"/>
       <c r="F19" s="11"/>
       <c r="G19" s="6"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="29"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="25"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -5470,8 +5840,8 @@
       <c r="E20" s="8"/>
       <c r="F20" s="13"/>
       <c r="G20" s="6"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="29"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="25"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -5481,7 +5851,7 @@
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="46"/>
+      <c r="H21" s="35"/>
       <c r="I21" s="11"/>
     </row>
     <row r="22" spans="1:9">
@@ -5492,7 +5862,7 @@
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="46"/>
+      <c r="H22" s="35"/>
       <c r="I22" s="11"/>
     </row>
     <row r="23" spans="1:9">
@@ -5503,7 +5873,7 @@
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
       <c r="G23" s="6"/>
-      <c r="H23" s="46"/>
+      <c r="H23" s="35"/>
       <c r="I23" s="11"/>
     </row>
     <row r="24" spans="1:9">
@@ -5514,7 +5884,7 @@
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
       <c r="G24" s="6"/>
-      <c r="H24" s="46"/>
+      <c r="H24" s="35"/>
       <c r="I24" s="11"/>
     </row>
     <row r="25" spans="1:9">
@@ -5525,7 +5895,7 @@
       <c r="E25" s="8"/>
       <c r="F25" s="9"/>
       <c r="G25" s="6"/>
-      <c r="H25" s="46"/>
+      <c r="H25" s="35"/>
       <c r="I25" s="11"/>
     </row>
     <row r="26" spans="1:9">
@@ -5536,7 +5906,7 @@
       <c r="E26" s="8"/>
       <c r="F26" s="9"/>
       <c r="G26" s="6"/>
-      <c r="H26" s="46"/>
+      <c r="H26" s="35"/>
       <c r="I26" s="11"/>
     </row>
     <row r="27" spans="1:9">
@@ -5547,7 +5917,7 @@
       <c r="E27" s="8"/>
       <c r="F27" s="9"/>
       <c r="G27" s="6"/>
-      <c r="H27" s="46"/>
+      <c r="H27" s="35"/>
       <c r="I27" s="11"/>
     </row>
     <row r="28" spans="1:9">
@@ -5558,7 +5928,7 @@
       <c r="E28" s="8"/>
       <c r="F28" s="9"/>
       <c r="G28" s="6"/>
-      <c r="H28" s="46"/>
+      <c r="H28" s="35"/>
       <c r="I28" s="11"/>
     </row>
     <row r="29" spans="1:9">
@@ -5569,7 +5939,7 @@
       <c r="E29" s="8"/>
       <c r="F29" s="9"/>
       <c r="G29" s="6"/>
-      <c r="H29" s="46"/>
+      <c r="H29" s="35"/>
       <c r="I29" s="11"/>
     </row>
     <row r="30" spans="1:9">
@@ -5580,7 +5950,7 @@
       <c r="E30" s="8"/>
       <c r="F30" s="9"/>
       <c r="G30" s="6"/>
-      <c r="H30" s="46"/>
+      <c r="H30" s="35"/>
       <c r="I30" s="11"/>
     </row>
     <row r="31" spans="1:9">
@@ -5591,7 +5961,7 @@
       <c r="E31" s="8"/>
       <c r="F31" s="9"/>
       <c r="G31" s="6"/>
-      <c r="H31" s="46"/>
+      <c r="H31" s="35"/>
       <c r="I31" s="11"/>
     </row>
     <row r="32" spans="1:9">
@@ -5602,7 +5972,7 @@
       <c r="E32" s="8"/>
       <c r="F32" s="9"/>
       <c r="G32" s="6"/>
-      <c r="H32" s="46"/>
+      <c r="H32" s="35"/>
       <c r="I32" s="11"/>
     </row>
     <row r="33" spans="1:9">
@@ -5613,7 +5983,7 @@
       <c r="E33" s="8"/>
       <c r="F33" s="9"/>
       <c r="G33" s="6"/>
-      <c r="H33" s="46"/>
+      <c r="H33" s="35"/>
       <c r="I33" s="11"/>
     </row>
   </sheetData>
@@ -5672,10 +6042,10 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="45" t="s">
+      <c r="H1" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="28" t="s">
         <v>8</v>
       </c>
     </row>
@@ -5683,40 +6053,40 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="23"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="8"/>
       <c r="F2" s="10"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="29"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="25"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="23"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="19"/>
       <c r="E3" s="8"/>
       <c r="F3" s="10"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="29"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="23"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="19"/>
       <c r="E4" s="8"/>
       <c r="F4" s="10"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="29"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -5724,12 +6094,12 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="23"/>
+      <c r="D5" s="19"/>
       <c r="E5" s="8"/>
       <c r="F5" s="10"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="29"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
@@ -5737,12 +6107,12 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="23"/>
+      <c r="D6" s="19"/>
       <c r="E6" s="8"/>
       <c r="F6" s="10"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="29"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
@@ -5750,12 +6120,12 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="23"/>
+      <c r="D7" s="19"/>
       <c r="E7" s="8"/>
       <c r="F7" s="10"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="29"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="25"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
@@ -5763,12 +6133,12 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="23"/>
+      <c r="D8" s="19"/>
       <c r="E8" s="8"/>
       <c r="F8" s="10"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="29"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="25"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
@@ -5776,12 +6146,12 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="23"/>
+      <c r="D9" s="19"/>
       <c r="E9" s="8"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="29"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="25"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
@@ -5789,12 +6159,12 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="23"/>
+      <c r="D10" s="19"/>
       <c r="E10" s="8"/>
       <c r="F10" s="10"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="29"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="25"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
@@ -5802,12 +6172,12 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="23"/>
+      <c r="D11" s="19"/>
       <c r="E11" s="8"/>
       <c r="F11" s="10"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="29"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="25"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
@@ -5815,12 +6185,12 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="23"/>
+      <c r="D12" s="19"/>
       <c r="E12" s="8"/>
       <c r="F12" s="10"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="29"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="25"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
@@ -5828,12 +6198,12 @@
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="23"/>
+      <c r="D13" s="19"/>
       <c r="E13" s="8"/>
       <c r="F13" s="10"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="29"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
@@ -5841,12 +6211,12 @@
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="23"/>
+      <c r="D14" s="19"/>
       <c r="E14" s="8"/>
       <c r="F14" s="10"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="29"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="25"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
@@ -5854,23 +6224,23 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="23"/>
+      <c r="D15" s="19"/>
       <c r="E15" s="8"/>
       <c r="F15" s="10"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="29"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="25"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="23"/>
+      <c r="D16" s="19"/>
       <c r="E16" s="8"/>
       <c r="F16" s="10"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="29"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="25"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6"/>
@@ -5880,8 +6250,8 @@
       <c r="E17" s="12"/>
       <c r="F17" s="10"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="29"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="25"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>
@@ -5891,8 +6261,8 @@
       <c r="E18" s="12"/>
       <c r="F18" s="10"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="29"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="25"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
@@ -5902,8 +6272,8 @@
       <c r="E19" s="12"/>
       <c r="F19" s="11"/>
       <c r="G19" s="6"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="29"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="25"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -5913,8 +6283,8 @@
       <c r="E20" s="8"/>
       <c r="F20" s="13"/>
       <c r="G20" s="6"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="29"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="25"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -5924,7 +6294,7 @@
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="46"/>
+      <c r="H21" s="35"/>
       <c r="I21" s="11"/>
     </row>
     <row r="22" spans="1:9">
@@ -5935,7 +6305,7 @@
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="46"/>
+      <c r="H22" s="35"/>
       <c r="I22" s="11"/>
     </row>
     <row r="23" spans="1:9">
@@ -5946,7 +6316,7 @@
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
       <c r="G23" s="6"/>
-      <c r="H23" s="46"/>
+      <c r="H23" s="35"/>
       <c r="I23" s="11"/>
     </row>
     <row r="24" spans="1:9">
@@ -5957,7 +6327,7 @@
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
       <c r="G24" s="6"/>
-      <c r="H24" s="46"/>
+      <c r="H24" s="35"/>
       <c r="I24" s="11"/>
     </row>
     <row r="25" spans="1:9">
@@ -5968,7 +6338,7 @@
       <c r="E25" s="8"/>
       <c r="F25" s="9"/>
       <c r="G25" s="6"/>
-      <c r="H25" s="46"/>
+      <c r="H25" s="35"/>
       <c r="I25" s="11"/>
     </row>
     <row r="26" spans="1:9">
@@ -5979,7 +6349,7 @@
       <c r="E26" s="8"/>
       <c r="F26" s="9"/>
       <c r="G26" s="6"/>
-      <c r="H26" s="46"/>
+      <c r="H26" s="35"/>
       <c r="I26" s="11"/>
     </row>
     <row r="27" spans="1:9">
@@ -5990,7 +6360,7 @@
       <c r="E27" s="8"/>
       <c r="F27" s="9"/>
       <c r="G27" s="6"/>
-      <c r="H27" s="46"/>
+      <c r="H27" s="35"/>
       <c r="I27" s="11"/>
     </row>
     <row r="28" spans="1:9">
@@ -6001,7 +6371,7 @@
       <c r="E28" s="8"/>
       <c r="F28" s="9"/>
       <c r="G28" s="6"/>
-      <c r="H28" s="46"/>
+      <c r="H28" s="35"/>
       <c r="I28" s="11"/>
     </row>
     <row r="29" spans="1:9">
@@ -6012,7 +6382,7 @@
       <c r="E29" s="8"/>
       <c r="F29" s="9"/>
       <c r="G29" s="6"/>
-      <c r="H29" s="46"/>
+      <c r="H29" s="35"/>
       <c r="I29" s="11"/>
     </row>
     <row r="30" spans="1:9">
@@ -6023,7 +6393,7 @@
       <c r="E30" s="8"/>
       <c r="F30" s="9"/>
       <c r="G30" s="6"/>
-      <c r="H30" s="46"/>
+      <c r="H30" s="35"/>
       <c r="I30" s="11"/>
     </row>
     <row r="31" spans="1:9">
@@ -6034,7 +6404,7 @@
       <c r="E31" s="8"/>
       <c r="F31" s="9"/>
       <c r="G31" s="6"/>
-      <c r="H31" s="46"/>
+      <c r="H31" s="35"/>
       <c r="I31" s="11"/>
     </row>
     <row r="32" spans="1:9">
@@ -6045,7 +6415,7 @@
       <c r="E32" s="8"/>
       <c r="F32" s="9"/>
       <c r="G32" s="6"/>
-      <c r="H32" s="46"/>
+      <c r="H32" s="35"/>
       <c r="I32" s="11"/>
     </row>
     <row r="33" spans="1:9">
@@ -6056,7 +6426,7 @@
       <c r="E33" s="8"/>
       <c r="F33" s="9"/>
       <c r="G33" s="6"/>
-      <c r="H33" s="46"/>
+      <c r="H33" s="35"/>
       <c r="I33" s="11"/>
     </row>
   </sheetData>

--- a/Treinamento/Index/Relatório de Recusas 02.02.2026 a 08.02.2026.xlsx
+++ b/Treinamento/Index/Relatório de Recusas 02.02.2026 a 08.02.2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29803"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29728"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/shirlei_witkowski_allianz_com_br/Documents/Planilha de recusa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F62C90C3-C1CA-4C84-A59C-82E86286022D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E6A7258-38FF-4455-976D-99FE613A4802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="02.02" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="297">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -892,6 +892,136 @@
   </si>
   <si>
     <t xml:space="preserve">JPBIA VENDAS ONLINE LTDA ME                  </t>
+  </si>
+  <si>
+    <t>ADRIANA PENAFIEL LUIZ CPF- 16184349856</t>
+  </si>
+  <si>
+    <t>Chassi irregular, favor corrigir</t>
+  </si>
+  <si>
+    <t>BERNARDINO CORREA DA SILVA CPF 95687122087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAFAEL SOARES BRANDAO                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEFFERSON DA SILVA PEDROSO                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAFAEL ALESSANDRE LISBOA RODRIGUES           </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Frente e lateral do passageiro, Porta malas aberto, Chassi, Frente e lateral do motorista, Traseira e lateral do passageiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOAVENTURA CARVALHO LIMA                     </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Documento da moto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTONIO ELIAS DA HORA JUNIOR                 </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Painel ligado, Chassi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSELEIA MANICA DESOSI                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULIANA ALINE GOULART                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUANNE DIAS FREITAS CARVALHO                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SINEIDE SANTOS SILVA                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERALDO ESTEVAO DA SILVA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIMONE FRANCO                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VINICIUS TADEU ROCHA FERNANDES               </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia completa da apólice referente 2025/2026 (Não será aceito a
+CI, uma vez em que a CBE não retorna os dados)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDELCIO GARCIA JUNIOR                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADEMIR ALVES MUNIZ                           </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 05.02.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRUNA DANIELLE SANTOS CIRQUEIRA              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO ROBERTO PEREIRA DE OLIVEIRA            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENATA MARIA GANDOLFO CAMPOS                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SEGURADO NÃO CORRIGIU AS FOTOS - PRAZO EXPIRADO FOTO: CHASSI, SEGURADO RECEBEU AS ORIENTAÇÕES E NÃO AS CUMPRIU, GERANDO A IMPOSSIBILIDADE EM FAZER UM REENVIO DEVIDO AO PRAZO LIMITE. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA REGINA DE PAULA FRANCA                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEBASTIAO JAIRO SILVA DE LIMA                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGAMENON GOMES MARTINS FILHO                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JHONNATHAN IANNIS MICHELON HAJIADONIOU       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DARIO APARECIDO MARQUEZ                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULIO CESAR DE JESUS CASTILHO                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NARISSON NERIS SILVA COSTA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALETE LIMA DA SILVA                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANESIO DE OLIVEIRA JUNIOR                    </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que a
+apólice consta ativa na congênere, para que possamos prosseguir
+coma liberação do bloqueio será necessário a apresentação do en
+dosso de cancelamento emitido, a atualização junto a Central de Bô
+nus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WALTER CAPINAM MACEDO FILHO                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO HENRIQUE URQUIZA DE CASTRO             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELISEU SILVA AZEDO                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JORGE DOUGLAS SOARES DE OLIVEIRA             </t>
+  </si>
+  <si>
+    <t>O veiculo já esta segurado conosco até 07/08/2026 por outro corretor, para
+seguir com uma nova apólice AZ e Santander, será necessário cancelar a apólice
+ativa e retransmitir como renovação não como Seguro Novo</t>
   </si>
 </sst>
 </file>
@@ -940,7 +1070,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -1166,12 +1296,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1305,12 +1446,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
@@ -5785,13 +5938,13 @@
       <c r="C2" s="18">
         <v>46058</v>
       </c>
-      <c r="D2" s="52">
+      <c r="D2" s="51">
         <v>136430571</v>
       </c>
-      <c r="E2" s="53">
+      <c r="E2" s="52">
         <v>3450231356</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="10" t="s">
         <v>216</v>
       </c>
       <c r="G2" s="48" t="s">
@@ -5814,13 +5967,13 @@
       <c r="C3" s="18">
         <v>46058</v>
       </c>
-      <c r="D3" s="52">
+      <c r="D3" s="51">
         <v>136457939</v>
       </c>
-      <c r="E3" s="53">
+      <c r="E3" s="52">
         <v>3450233248</v>
       </c>
-      <c r="F3" s="51" t="s">
+      <c r="F3" s="10" t="s">
         <v>218</v>
       </c>
       <c r="G3" s="48" t="s">
@@ -5843,13 +5996,13 @@
       <c r="C4" s="18">
         <v>46058</v>
       </c>
-      <c r="D4" s="52">
+      <c r="D4" s="51">
         <v>136471107</v>
       </c>
-      <c r="E4" s="53">
+      <c r="E4" s="52">
         <v>3450234502</v>
       </c>
-      <c r="F4" s="51" t="s">
+      <c r="F4" s="10" t="s">
         <v>220</v>
       </c>
       <c r="G4" s="48" t="s">
@@ -5872,13 +6025,13 @@
       <c r="C5" s="18">
         <v>46058</v>
       </c>
-      <c r="D5" s="52">
+      <c r="D5" s="51">
         <v>136480400</v>
       </c>
-      <c r="E5" s="53">
+      <c r="E5" s="52">
         <v>3450235107</v>
       </c>
-      <c r="F5" s="51" t="s">
+      <c r="F5" s="10" t="s">
         <v>221</v>
       </c>
       <c r="G5" s="48" t="s">
@@ -5901,13 +6054,13 @@
       <c r="C6" s="18">
         <v>46058</v>
       </c>
-      <c r="D6" s="52">
+      <c r="D6" s="51">
         <v>136480845</v>
       </c>
-      <c r="E6" s="53">
+      <c r="E6" s="52">
         <v>3450235130</v>
       </c>
-      <c r="F6" s="51" t="s">
+      <c r="F6" s="10" t="s">
         <v>222</v>
       </c>
       <c r="G6" s="48" t="s">
@@ -5930,13 +6083,13 @@
       <c r="C7" s="18">
         <v>46058</v>
       </c>
-      <c r="D7" s="52">
+      <c r="D7" s="51">
         <v>136483174</v>
       </c>
-      <c r="E7" s="53">
+      <c r="E7" s="52">
         <v>3450235350</v>
       </c>
-      <c r="F7" s="51" t="s">
+      <c r="F7" s="10" t="s">
         <v>224</v>
       </c>
       <c r="G7" s="48" t="s">
@@ -5959,13 +6112,13 @@
       <c r="C8" s="18">
         <v>46058</v>
       </c>
-      <c r="D8" s="52">
+      <c r="D8" s="51">
         <v>136491426</v>
       </c>
-      <c r="E8" s="53">
+      <c r="E8" s="52">
         <v>3450236097</v>
       </c>
-      <c r="F8" s="51" t="s">
+      <c r="F8" s="10" t="s">
         <v>226</v>
       </c>
       <c r="G8" s="48" t="s">
@@ -5988,19 +6141,19 @@
       <c r="C9" s="18">
         <v>46058</v>
       </c>
-      <c r="D9" s="52">
+      <c r="D9" s="51">
         <v>136492138</v>
       </c>
-      <c r="E9" s="53">
+      <c r="E9" s="52">
         <v>3450236207</v>
       </c>
-      <c r="F9" s="51" t="s">
+      <c r="F9" s="10" t="s">
         <v>228</v>
       </c>
       <c r="G9" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="54" t="s">
+      <c r="H9" s="35" t="s">
         <v>229</v>
       </c>
       <c r="I9" s="25">
@@ -6017,13 +6170,13 @@
       <c r="C10" s="18">
         <v>46058</v>
       </c>
-      <c r="D10" s="52">
+      <c r="D10" s="51">
         <v>136494955</v>
       </c>
-      <c r="E10" s="53">
+      <c r="E10" s="52">
         <v>3450236581</v>
       </c>
-      <c r="F10" s="51" t="s">
+      <c r="F10" s="10" t="s">
         <v>230</v>
       </c>
       <c r="G10" s="48" t="s">
@@ -6046,13 +6199,13 @@
       <c r="C11" s="18">
         <v>46058</v>
       </c>
-      <c r="D11" s="52">
+      <c r="D11" s="51">
         <v>136494531</v>
       </c>
-      <c r="E11" s="53">
+      <c r="E11" s="52">
         <v>3450236526</v>
       </c>
-      <c r="F11" s="51" t="s">
+      <c r="F11" s="10" t="s">
         <v>232</v>
       </c>
       <c r="G11" s="48" t="s">
@@ -6075,13 +6228,13 @@
       <c r="C12" s="18">
         <v>46058</v>
       </c>
-      <c r="D12" s="52">
+      <c r="D12" s="51">
         <v>136477170</v>
       </c>
-      <c r="E12" s="53">
+      <c r="E12" s="52">
         <v>3450234920</v>
       </c>
-      <c r="F12" s="51" t="s">
+      <c r="F12" s="10" t="s">
         <v>234</v>
       </c>
       <c r="G12" s="48" t="s">
@@ -6104,19 +6257,19 @@
       <c r="C13" s="18">
         <v>46058</v>
       </c>
-      <c r="D13" s="52">
+      <c r="D13" s="51">
         <v>136487155</v>
       </c>
-      <c r="E13" s="53">
+      <c r="E13" s="52">
         <v>3450235778</v>
       </c>
-      <c r="F13" s="51" t="s">
+      <c r="F13" s="10" t="s">
         <v>236</v>
       </c>
       <c r="G13" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="H13" s="54" t="s">
+      <c r="H13" s="35" t="s">
         <v>237</v>
       </c>
       <c r="I13" s="25">
@@ -6133,13 +6286,13 @@
       <c r="C14" s="18">
         <v>46058</v>
       </c>
-      <c r="D14" s="52">
+      <c r="D14" s="51">
         <v>136490933</v>
       </c>
-      <c r="E14" s="53">
+      <c r="E14" s="52">
         <v>3450236053</v>
       </c>
-      <c r="F14" s="51" t="s">
+      <c r="F14" s="10" t="s">
         <v>238</v>
       </c>
       <c r="G14" s="48" t="s">
@@ -6162,13 +6315,13 @@
       <c r="C15" s="18">
         <v>46058</v>
       </c>
-      <c r="D15" s="52">
+      <c r="D15" s="51">
         <v>136491341</v>
       </c>
-      <c r="E15" s="53">
+      <c r="E15" s="52">
         <v>3450236075</v>
       </c>
-      <c r="F15" s="51" t="s">
+      <c r="F15" s="10" t="s">
         <v>97</v>
       </c>
       <c r="G15" s="49" t="s">
@@ -6191,13 +6344,13 @@
       <c r="C16" s="18">
         <v>46058</v>
       </c>
-      <c r="D16" s="52">
+      <c r="D16" s="51">
         <v>136494857</v>
       </c>
-      <c r="E16" s="53">
+      <c r="E16" s="52">
         <v>3450236560</v>
       </c>
-      <c r="F16" s="51" t="s">
+      <c r="F16" s="10" t="s">
         <v>240</v>
       </c>
       <c r="G16" s="49" t="s">
@@ -6220,19 +6373,19 @@
       <c r="C17" s="18">
         <v>46058</v>
       </c>
-      <c r="D17" s="52">
+      <c r="D17" s="51">
         <v>136505741</v>
       </c>
-      <c r="E17" s="53">
+      <c r="E17" s="52">
         <v>3450237142</v>
       </c>
-      <c r="F17" s="51" t="s">
+      <c r="F17" s="10" t="s">
         <v>242</v>
       </c>
       <c r="G17" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="54" t="s">
+      <c r="H17" s="35" t="s">
         <v>243</v>
       </c>
       <c r="I17" s="25">
@@ -6249,13 +6402,13 @@
       <c r="C18" s="18">
         <v>46058</v>
       </c>
-      <c r="D18" s="52">
+      <c r="D18" s="51">
         <v>136508214</v>
       </c>
-      <c r="E18" s="53">
+      <c r="E18" s="52">
         <v>3450237340</v>
       </c>
-      <c r="F18" s="51" t="s">
+      <c r="F18" s="10" t="s">
         <v>244</v>
       </c>
       <c r="G18" s="49" t="s">
@@ -6278,13 +6431,13 @@
       <c r="C19" s="18">
         <v>46058</v>
       </c>
-      <c r="D19" s="52">
+      <c r="D19" s="51">
         <v>136545742</v>
       </c>
-      <c r="E19" s="53">
+      <c r="E19" s="52">
         <v>3450239892</v>
       </c>
-      <c r="F19" s="51" t="s">
+      <c r="F19" s="10" t="s">
         <v>246</v>
       </c>
       <c r="G19" s="49" t="s">
@@ -6307,13 +6460,13 @@
       <c r="C20" s="18">
         <v>46058</v>
       </c>
-      <c r="D20" s="52">
+      <c r="D20" s="51">
         <v>136555173</v>
       </c>
-      <c r="E20" s="53">
+      <c r="E20" s="52">
         <v>3450240981</v>
       </c>
-      <c r="F20" s="51" t="s">
+      <c r="F20" s="10" t="s">
         <v>247</v>
       </c>
       <c r="G20" s="49" t="s">
@@ -6336,19 +6489,19 @@
       <c r="C21" s="18">
         <v>46058</v>
       </c>
-      <c r="D21" s="52">
+      <c r="D21" s="51">
         <v>136361533</v>
       </c>
-      <c r="E21" s="53">
+      <c r="E21" s="52">
         <v>3450225867</v>
       </c>
-      <c r="F21" s="51" t="s">
+      <c r="F21" s="10" t="s">
         <v>248</v>
       </c>
       <c r="G21" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="H21" s="54" t="s">
+      <c r="H21" s="35" t="s">
         <v>249</v>
       </c>
       <c r="I21" s="25">
@@ -6365,13 +6518,13 @@
       <c r="C22" s="18">
         <v>46058</v>
       </c>
-      <c r="D22" s="52">
+      <c r="D22" s="51">
         <v>136432105</v>
       </c>
-      <c r="E22" s="53">
+      <c r="E22" s="52">
         <v>3450231499</v>
       </c>
-      <c r="F22" s="51" t="s">
+      <c r="F22" s="10" t="s">
         <v>250</v>
       </c>
       <c r="G22" s="49" t="s">
@@ -6394,13 +6547,13 @@
       <c r="C23" s="18">
         <v>46058</v>
       </c>
-      <c r="D23" s="52">
+      <c r="D23" s="51">
         <v>136464388</v>
       </c>
-      <c r="E23" s="53">
+      <c r="E23" s="52">
         <v>3450234030</v>
       </c>
-      <c r="F23" s="51" t="s">
+      <c r="F23" s="10" t="s">
         <v>251</v>
       </c>
       <c r="G23" s="49" t="s">
@@ -6423,13 +6576,13 @@
       <c r="C24" s="18">
         <v>46058</v>
       </c>
-      <c r="D24" s="52">
+      <c r="D24" s="51">
         <v>136490384</v>
       </c>
-      <c r="E24" s="53">
+      <c r="E24" s="52">
         <v>3450236010</v>
       </c>
-      <c r="F24" s="51" t="s">
+      <c r="F24" s="10" t="s">
         <v>252</v>
       </c>
       <c r="G24" s="49" t="s">
@@ -6452,13 +6605,13 @@
       <c r="C25" s="18">
         <v>46058</v>
       </c>
-      <c r="D25" s="52">
+      <c r="D25" s="51">
         <v>136449849</v>
       </c>
-      <c r="E25" s="53">
+      <c r="E25" s="52">
         <v>3450232962</v>
       </c>
-      <c r="F25" s="51" t="s">
+      <c r="F25" s="10" t="s">
         <v>76</v>
       </c>
       <c r="G25" s="49" t="s">
@@ -6481,13 +6634,13 @@
       <c r="C26" s="18">
         <v>46058</v>
       </c>
-      <c r="D26" s="52">
+      <c r="D26" s="51">
         <v>136401544</v>
       </c>
-      <c r="E26" s="53">
+      <c r="E26" s="52">
         <v>3450228584</v>
       </c>
-      <c r="F26" s="51" t="s">
+      <c r="F26" s="10" t="s">
         <v>254</v>
       </c>
       <c r="G26" s="49" t="s">
@@ -6510,13 +6663,13 @@
       <c r="C27" s="18">
         <v>46058</v>
       </c>
-      <c r="D27" s="52">
+      <c r="D27" s="51">
         <v>136492769</v>
       </c>
-      <c r="E27" s="53">
+      <c r="E27" s="52">
         <v>3450236262</v>
       </c>
-      <c r="F27" s="51" t="s">
+      <c r="F27" s="10" t="s">
         <v>255</v>
       </c>
       <c r="G27" s="49" t="s">
@@ -6582,8 +6735,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE4070E6-0057-46A0-809E-7FFD1075DDF6}">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.28515625" customWidth="1"/>
+    <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
@@ -6618,393 +6782,966 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="35"/>
+      <c r="B2" s="18">
+        <v>46058</v>
+      </c>
+      <c r="C2" s="54">
+        <v>46059</v>
+      </c>
+      <c r="D2" s="55" t="s">
+        <v>158</v>
+      </c>
+      <c r="E2" s="15">
+        <v>3450241740</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="35" t="s">
+        <v>257</v>
+      </c>
       <c r="I2" s="25"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="35"/>
+      <c r="B3" s="18">
+        <v>46058</v>
+      </c>
+      <c r="C3" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="E3" s="15">
+        <v>3450241850</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="G3" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="35" t="s">
+        <v>257</v>
+      </c>
       <c r="I3" s="25"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="25"/>
+      <c r="B4" s="18">
+        <v>46048</v>
+      </c>
+      <c r="C4" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D4" s="56">
+        <v>136419479</v>
+      </c>
+      <c r="E4" s="15">
+        <v>3450230465</v>
+      </c>
+      <c r="F4" s="53" t="s">
+        <v>259</v>
+      </c>
+      <c r="G4" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="25">
+        <v>46048</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="25"/>
+      <c r="B5" s="18">
+        <v>46049</v>
+      </c>
+      <c r="C5" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D5" s="56">
+        <v>136422602</v>
+      </c>
+      <c r="E5" s="15">
+        <v>3450230696</v>
+      </c>
+      <c r="F5" s="53" t="s">
+        <v>260</v>
+      </c>
+      <c r="G5" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="25">
+        <v>46049</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="25"/>
+      <c r="B6" s="18">
+        <v>46052</v>
+      </c>
+      <c r="C6" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D6" s="56">
+        <v>136499722</v>
+      </c>
+      <c r="E6" s="15">
+        <v>3450235460</v>
+      </c>
+      <c r="F6" s="53" t="s">
+        <v>261</v>
+      </c>
+      <c r="G6" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="35" t="s">
+        <v>262</v>
+      </c>
+      <c r="I6" s="25">
+        <v>46052</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="25"/>
+      <c r="B7" s="18">
+        <v>46053</v>
+      </c>
+      <c r="C7" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D7" s="56">
+        <v>136500176</v>
+      </c>
+      <c r="E7" s="15">
+        <v>3450236911</v>
+      </c>
+      <c r="F7" s="53" t="s">
+        <v>263</v>
+      </c>
+      <c r="G7" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="35" t="s">
+        <v>264</v>
+      </c>
+      <c r="I7" s="25">
+        <v>46053</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="25"/>
+      <c r="B8" s="18">
+        <v>46053</v>
+      </c>
+      <c r="C8" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D8" s="56">
+        <v>136498096</v>
+      </c>
+      <c r="E8" s="15">
+        <v>3450236856</v>
+      </c>
+      <c r="F8" s="53" t="s">
+        <v>265</v>
+      </c>
+      <c r="G8" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="35" t="s">
+        <v>266</v>
+      </c>
+      <c r="I8" s="25">
+        <v>46053</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="25"/>
+      <c r="B9" s="18">
+        <v>46056</v>
+      </c>
+      <c r="C9" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D9" s="56">
+        <v>136537250</v>
+      </c>
+      <c r="E9" s="15">
+        <v>3450239584</v>
+      </c>
+      <c r="F9" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="G9" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9" s="25">
+        <v>46056</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="25"/>
+      <c r="B10" s="18">
+        <v>46052</v>
+      </c>
+      <c r="C10" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D10" s="56">
+        <v>136499664</v>
+      </c>
+      <c r="E10" s="15">
+        <v>3450235811</v>
+      </c>
+      <c r="F10" s="53" t="s">
+        <v>268</v>
+      </c>
+      <c r="G10" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" s="25">
+        <v>46052</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="25"/>
+      <c r="B11" s="18">
+        <v>46057</v>
+      </c>
+      <c r="C11" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D11" s="56">
+        <v>136556944</v>
+      </c>
+      <c r="E11" s="15">
+        <v>3450241157</v>
+      </c>
+      <c r="F11" s="53" t="s">
+        <v>269</v>
+      </c>
+      <c r="G11" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11" s="25">
+        <v>46057</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="25"/>
+      <c r="B12" s="18">
+        <v>46058</v>
+      </c>
+      <c r="C12" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D12" s="56">
+        <v>136575042</v>
+      </c>
+      <c r="E12" s="15">
+        <v>3450242642</v>
+      </c>
+      <c r="F12" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="G12" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12" s="25">
+        <v>46058</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="25"/>
+      <c r="B13" s="18">
+        <v>46058</v>
+      </c>
+      <c r="C13" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D13" s="56">
+        <v>136576778</v>
+      </c>
+      <c r="E13" s="15">
+        <v>3450242807</v>
+      </c>
+      <c r="F13" s="53" t="s">
+        <v>271</v>
+      </c>
+      <c r="G13" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="I13" s="25">
+        <v>46058</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="25"/>
+      <c r="B14" s="18">
+        <v>46058</v>
+      </c>
+      <c r="C14" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D14" s="56">
+        <v>136573520</v>
+      </c>
+      <c r="E14" s="15">
+        <v>3450242488</v>
+      </c>
+      <c r="F14" s="53" t="s">
+        <v>272</v>
+      </c>
+      <c r="G14" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="I14" s="25">
+        <v>46058</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="25"/>
+      <c r="B15" s="18">
+        <v>46052</v>
+      </c>
+      <c r="C15" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D15" s="56">
+        <v>136399342</v>
+      </c>
+      <c r="E15" s="15">
+        <v>3450229112</v>
+      </c>
+      <c r="F15" s="53" t="s">
+        <v>273</v>
+      </c>
+      <c r="G15" s="48" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="58" t="s">
+        <v>274</v>
+      </c>
+      <c r="I15" s="25">
+        <v>46049</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="25"/>
+      <c r="A16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="18">
+        <v>46050</v>
+      </c>
+      <c r="C16" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D16" s="56">
+        <v>136449074</v>
+      </c>
+      <c r="E16" s="15">
+        <v>3450232885</v>
+      </c>
+      <c r="F16" s="53" t="s">
+        <v>275</v>
+      </c>
+      <c r="G16" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" s="25">
+        <v>46050</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="25"/>
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="18">
+        <v>46051</v>
+      </c>
+      <c r="C17" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D17" s="56">
+        <v>136473015</v>
+      </c>
+      <c r="E17" s="15">
+        <v>3450234678</v>
+      </c>
+      <c r="F17" s="53" t="s">
+        <v>276</v>
+      </c>
+      <c r="G17" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="35" t="s">
+        <v>277</v>
+      </c>
+      <c r="I17" s="25">
+        <v>46058</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="25"/>
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="18">
+        <v>46049</v>
+      </c>
+      <c r="C18" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D18" s="56">
+        <v>136424014</v>
+      </c>
+      <c r="E18" s="15">
+        <v>3450230784</v>
+      </c>
+      <c r="F18" s="53" t="s">
+        <v>278</v>
+      </c>
+      <c r="G18" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" s="35" t="s">
+        <v>277</v>
+      </c>
+      <c r="I18" s="25">
+        <v>46058</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="25"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="18">
+        <v>46052</v>
+      </c>
+      <c r="C19" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D19" s="56">
+        <v>136480143</v>
+      </c>
+      <c r="E19" s="15">
+        <v>3450235063</v>
+      </c>
+      <c r="F19" s="53" t="s">
+        <v>279</v>
+      </c>
+      <c r="G19" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="H19" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="I19" s="25">
+        <v>46052</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="25"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="18">
+        <v>46052</v>
+      </c>
+      <c r="C20" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D20" s="56">
+        <v>136484935</v>
+      </c>
+      <c r="E20" s="15">
+        <v>3450235613</v>
+      </c>
+      <c r="F20" s="53" t="s">
+        <v>280</v>
+      </c>
+      <c r="G20" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" s="35" t="s">
+        <v>281</v>
+      </c>
+      <c r="I20" s="25">
+        <v>46052</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="11"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="18">
+        <v>46048</v>
+      </c>
+      <c r="C21" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D21" s="56">
+        <v>136422367</v>
+      </c>
+      <c r="E21" s="15">
+        <v>3450229497</v>
+      </c>
+      <c r="F21" s="53" t="s">
+        <v>282</v>
+      </c>
+      <c r="G21" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" s="25">
+        <v>46048</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="11"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="18">
+        <v>46049</v>
+      </c>
+      <c r="C22" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D22" s="56">
+        <v>136422868</v>
+      </c>
+      <c r="E22" s="15">
+        <v>3450230729</v>
+      </c>
+      <c r="F22" s="53" t="s">
+        <v>283</v>
+      </c>
+      <c r="G22" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="I22" s="25">
+        <v>46049</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="11"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="18">
+        <v>46049</v>
+      </c>
+      <c r="C23" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D23" s="56">
+        <v>136425177</v>
+      </c>
+      <c r="E23" s="15">
+        <v>3450230872</v>
+      </c>
+      <c r="F23" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="G23" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="I23" s="25">
+        <v>46049</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="11"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="18">
+        <v>46049</v>
+      </c>
+      <c r="C24" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D24" s="56">
+        <v>136425594</v>
+      </c>
+      <c r="E24" s="15">
+        <v>3450230927</v>
+      </c>
+      <c r="F24" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="G24" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H24" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="I24" s="25">
+        <v>46049</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="11"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="18">
+        <v>46049</v>
+      </c>
+      <c r="C25" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D25" s="56">
+        <v>136426215</v>
+      </c>
+      <c r="E25" s="15">
+        <v>3450231015</v>
+      </c>
+      <c r="F25" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G25" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H25" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="I25" s="25">
+        <v>46049</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="11"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="18">
+        <v>46049</v>
+      </c>
+      <c r="C26" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D26" s="56">
+        <v>136426234</v>
+      </c>
+      <c r="E26" s="15">
+        <v>3450231026</v>
+      </c>
+      <c r="F26" s="53" t="s">
+        <v>287</v>
+      </c>
+      <c r="G26" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H26" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="I26" s="25">
+        <v>46049</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="11"/>
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="18">
+        <v>46049</v>
+      </c>
+      <c r="C27" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D27" s="56">
+        <v>136426571</v>
+      </c>
+      <c r="E27" s="15">
+        <v>3450231070</v>
+      </c>
+      <c r="F27" s="53" t="s">
+        <v>288</v>
+      </c>
+      <c r="G27" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H27" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="I27" s="25">
+        <v>46049</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="11"/>
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="18">
+        <v>46049</v>
+      </c>
+      <c r="C28" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D28" s="56">
+        <v>136426694</v>
+      </c>
+      <c r="E28" s="15">
+        <v>3450231092</v>
+      </c>
+      <c r="F28" s="53" t="s">
+        <v>288</v>
+      </c>
+      <c r="G28" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H28" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="I28" s="25">
+        <v>46049</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="11"/>
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="18">
+        <v>46049</v>
+      </c>
+      <c r="C29" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D29" s="56">
+        <v>136427067</v>
+      </c>
+      <c r="E29" s="15">
+        <v>3450231158</v>
+      </c>
+      <c r="F29" s="53" t="s">
+        <v>289</v>
+      </c>
+      <c r="G29" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H29" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="I29" s="25">
+        <v>46049</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="11"/>
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="18">
+        <v>46049</v>
+      </c>
+      <c r="C30" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D30" s="56">
+        <v>136428683</v>
+      </c>
+      <c r="E30" s="15">
+        <v>3450231268</v>
+      </c>
+      <c r="F30" s="53" t="s">
+        <v>290</v>
+      </c>
+      <c r="G30" s="48" t="s">
+        <v>17</v>
+      </c>
+      <c r="H30" s="58" t="s">
+        <v>291</v>
+      </c>
+      <c r="I30" s="25">
+        <v>46049</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="11"/>
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="18">
+        <v>46049</v>
+      </c>
+      <c r="C31" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D31" s="56">
+        <v>136430360</v>
+      </c>
+      <c r="E31" s="15">
+        <v>3450231334</v>
+      </c>
+      <c r="F31" s="53" t="s">
+        <v>292</v>
+      </c>
+      <c r="G31" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H31" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="I31" s="25">
+        <v>46049</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="11"/>
+      <c r="A32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="18">
+        <v>46049</v>
+      </c>
+      <c r="C32" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D32" s="56">
+        <v>136433937</v>
+      </c>
+      <c r="E32" s="15">
+        <v>3450231741</v>
+      </c>
+      <c r="F32" s="53" t="s">
+        <v>293</v>
+      </c>
+      <c r="G32" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="H32" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="I32" s="25">
+        <v>46049</v>
+      </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="6"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="35"/>
-      <c r="I33" s="11"/>
+      <c r="A33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="18">
+        <v>46049</v>
+      </c>
+      <c r="C33" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D33" s="56">
+        <v>136435029</v>
+      </c>
+      <c r="E33" s="15">
+        <v>3450231884</v>
+      </c>
+      <c r="F33" s="53" t="s">
+        <v>97</v>
+      </c>
+      <c r="G33" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="H33" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="I33" s="25">
+        <v>46049</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="18">
+        <v>46049</v>
+      </c>
+      <c r="C34" s="25">
+        <v>46059</v>
+      </c>
+      <c r="D34" s="56">
+        <v>136435842</v>
+      </c>
+      <c r="E34" s="15">
+        <v>3450231972</v>
+      </c>
+      <c r="F34" s="53" t="s">
+        <v>294</v>
+      </c>
+      <c r="G34" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="H34" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="I34" s="25">
+        <v>46049</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="1">
+    <cfRule type="notContainsBlanks" priority="4">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{2865F2D2-F129-4AA9-986B-1E489BEC1137}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A34" xr:uid="{2865F2D2-F129-4AA9-986B-1E489BEC1137}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{6E894C12-A235-4CC0-941E-DDB9E76595EF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G34" xr:uid="{6E894C12-A235-4CC0-941E-DDB9E76595EF}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7014,7 +7751,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C0FECCA-654E-4E2D-951A-47E70A94C04C}">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.28515625" customWidth="1"/>
@@ -7061,34 +7798,46 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="25"/>
+      <c r="B2" s="18">
+        <v>46049</v>
+      </c>
+      <c r="C2" s="18">
+        <v>46060</v>
+      </c>
+      <c r="D2" s="56">
+        <v>136424431</v>
+      </c>
+      <c r="E2" s="15">
+        <v>3450230839</v>
+      </c>
+      <c r="F2" s="53" t="s">
+        <v>295</v>
+      </c>
+      <c r="G2" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="58" t="s">
+        <v>296</v>
+      </c>
+      <c r="I2" s="25">
+        <v>46051</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A3" s="6"/>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="10"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="22"/>
       <c r="G3" s="20"/>
       <c r="H3" s="35"/>
       <c r="I3" s="25"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
       <c r="D4" s="19"/>
       <c r="E4" s="8"/>
       <c r="F4" s="10"/>
@@ -7097,9 +7846,7 @@
       <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A5" s="6"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
       <c r="D5" s="19"/>
@@ -7110,9 +7857,7 @@
       <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A6" s="6"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="19"/>
@@ -7122,321 +7867,6 @@
       <c r="H6" s="35"/>
       <c r="I6" s="25"/>
     </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="25"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="25"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="25"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="25"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="25"/>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="25"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="25"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="25"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="25"/>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="25"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="25"/>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="25"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="25"/>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="25"/>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="11"/>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="11"/>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="11"/>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="11"/>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="11"/>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="11"/>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="11"/>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="11"/>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="11"/>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="11"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="11"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="11"/>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="6"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="35"/>
-      <c r="I33" s="11"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
     <cfRule type="notContainsBlanks" priority="1">
@@ -7444,10 +7874,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{103C6060-74E3-4A29-8162-ED0DCC298E89}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A6" xr:uid="{103C6060-74E3-4A29-8162-ED0DCC298E89}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{FEA98D3B-5781-4696-A128-BE76CB777022}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G6" xr:uid="{FEA98D3B-5781-4696-A128-BE76CB777022}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7506,10 +7936,10 @@
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="20"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="48"/>
       <c r="H2" s="35"/>
       <c r="I2" s="25"/>
     </row>
@@ -7519,10 +7949,10 @@
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="20"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="48"/>
       <c r="H3" s="35"/>
       <c r="I3" s="25"/>
     </row>
@@ -7532,9 +7962,9 @@
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="10"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="22"/>
       <c r="G4" s="20"/>
       <c r="H4" s="35"/>
       <c r="I4" s="25"/>
@@ -7899,65 +8329,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="45" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="06364c42bcbf61016b6bd5e32d4d0782">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="199c6c2eefa6ec2f672a95412cfea747" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -8341,6 +8712,65 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -8385,7 +8815,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC664629-FB30-4E50-90C0-4DA45DF2C121}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8393,7 +8823,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC664629-FB30-4E50-90C0-4DA45DF2C121}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
